--- a/src/attributions/attributions_saliency_traj_398.xlsx
+++ b/src/attributions/attributions_saliency_traj_398.xlsx
@@ -1568,1140 +1568,1140 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.009242469444870949</v>
+        <v>0.01470690499991179</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04719144105911255</v>
+        <v>0.1253307461738586</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001829421147704124</v>
+        <v>0.07597220689058304</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01677962765097618</v>
+        <v>0.02272682450711727</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001380348112434149</v>
+        <v>0.03083714842796326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01129090785980225</v>
+        <v>0.1180619448423386</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002183133736252785</v>
+        <v>0.02173436246812344</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008550766506232321</v>
+        <v>0.001490537077188492</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001573714194819331</v>
+        <v>0.05530276894569397</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008047749288380146</v>
+        <v>0.01257530506700277</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03050791658461094</v>
+        <v>0.1497039198875427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005463689565658569</v>
+        <v>0.06871779263019562</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02139485254883766</v>
+        <v>0.001995578408241272</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01145896594971418</v>
+        <v>0.0242924764752388</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01661901734769344</v>
+        <v>0.09782934188842773</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009133925661444664</v>
+        <v>0.009543527849018574</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01611190848052502</v>
+        <v>0.04076965898275375</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009547774097882211</v>
+        <v>0.04717068746685982</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001750265480950475</v>
+        <v>4.788441583514214e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007008224725723267</v>
+        <v>0.04310604929924011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004825811483897269</v>
+        <v>0.003388562006875873</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003046864178031683</v>
+        <v>0.01468757726252079</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004874542355537415</v>
+        <v>0.01681582257151604</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002267434494569898</v>
+        <v>0.005207512993365526</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00410783663392067</v>
+        <v>0.01669096946716309</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.003427189774811268</v>
+        <v>0.01360472571104765</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004586776718497276</v>
+        <v>0.003852466819807887</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000165876466780901</v>
+        <v>0.00349707156419754</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.006394084077328444</v>
+        <v>0.02349995635449886</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001669270801357925</v>
+        <v>0.03500295430421829</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005722759291529655</v>
+        <v>0.01312904339283705</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003436914179474115</v>
+        <v>0.04105333238840103</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002020917367190123</v>
+        <v>0.0298198014497757</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.008198517374694347</v>
+        <v>0.01651888340711594</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.562087219208479e-05</v>
+        <v>0.07621669769287109</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0005609873333014548</v>
+        <v>0.01019807532429695</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.006040895357728004</v>
+        <v>0.01219922956079245</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.007197453640401363</v>
+        <v>0.05000326409935951</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001011937973089516</v>
+        <v>0.005745891481637955</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.002016299404203892</v>
+        <v>0.004652468487620354</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0005456043290905654</v>
+        <v>0.05362869799137115</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.005538396071642637</v>
+        <v>0.01338228397071362</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001119124935939908</v>
+        <v>0.0109693119302392</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001624273834750056</v>
+        <v>0.03832197189331055</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.083298750221729e-05</v>
+        <v>0.007090804167091846</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.006524421740323305</v>
+        <v>0.01179685164242983</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.03939658403396606</v>
+        <v>0.1532918214797974</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.001175804529339075</v>
+        <v>0.05041791498661041</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001835416071116924</v>
+        <v>0.03101428970694542</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.01879245042800903</v>
+        <v>0.05032261833548546</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0007737695705145597</v>
+        <v>0.05678404122591019</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.00377738056704402</v>
+        <v>0.02171848900616169</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.005548976361751556</v>
+        <v>0.03965209797024727</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0008898950763978064</v>
+        <v>0.003804883919656277</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.003657993860542774</v>
+        <v>0.002752520143985748</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.005815105512738228</v>
+        <v>0.06601759791374207</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.005168454721570015</v>
+        <v>0.01653297245502472</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0008277107845060527</v>
+        <v>0.01107672415673733</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01300884503871202</v>
+        <v>0.05663555115461349</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.004779055248945951</v>
+        <v>0.01117955334484577</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.004816003143787384</v>
+        <v>0.0008446499705314636</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.009241526946425438</v>
+        <v>0.02657509595155716</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.001898937160149217</v>
+        <v>0.02223098464310169</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.007079124450683594</v>
+        <v>0.004861504770815372</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.008498986251652241</v>
+        <v>0.005062676034867764</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001551217515952885</v>
+        <v>0.006742328405380249</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.01104951836168766</v>
+        <v>0.00743099395185709</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.01085963938385248</v>
+        <v>0.01500696875154972</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0004870701231993735</v>
+        <v>0.04437587782740593</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0005268910899758339</v>
+        <v>0.02608274668455124</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002577770734205842</v>
+        <v>0.01404411811381578</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.001304588280618191</v>
+        <v>0.02528865449130535</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.00520769041031599</v>
+        <v>0.01990446634590626</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01824897527694702</v>
+        <v>0.1527872532606125</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0001079155917977914</v>
+        <v>0.01275153085589409</v>
       </c>
       <c r="BX3" t="n">
-        <v>9.29390371311456e-05</v>
+        <v>0.0003692973405122757</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.001135080470703542</v>
+        <v>0.03561414778232574</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.009482575580477715</v>
+        <v>0.03232356905937195</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.001256315386854112</v>
+        <v>0.007045466918498278</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.001552364556118846</v>
+        <v>0.01890686713159084</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.003210107563063502</v>
+        <v>0.01067021396011114</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.003841682802885771</v>
+        <v>0.01157098263502121</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.008341759443283081</v>
+        <v>0.03598481416702271</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.001960596302524209</v>
+        <v>0.006240678019821644</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.00422391714528203</v>
+        <v>0.004405487794429064</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.002121519763022661</v>
+        <v>0.0242449939250946</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.002211259678006172</v>
+        <v>0.02265827730298042</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00272528943605721</v>
+        <v>0.006135242059826851</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.000207059842068702</v>
+        <v>0.01054962351918221</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.001551399356685579</v>
+        <v>0.004553764127194881</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.005693033803254366</v>
+        <v>0.01783544383943081</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.005010718479752541</v>
+        <v>0.0291246622800827</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.00421373825520277</v>
+        <v>0.02865783683955669</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.00902077928185463</v>
+        <v>0.008615989238023758</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.01161062065511942</v>
+        <v>0.009386280551552773</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.009983308613300323</v>
+        <v>0.05101927742362022</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.001750605995766819</v>
+        <v>0.00102798268198967</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.005301119294017553</v>
+        <v>0.0005983333103358746</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0009762049303390086</v>
+        <v>0.002775886794552207</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.003241928294301033</v>
+        <v>0.0002716609742492437</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.006385174114257097</v>
+        <v>0.03278862684965134</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.002237681997939944</v>
+        <v>0.01224460080265999</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.00644703721627593</v>
+        <v>0.003712952602654696</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.001956173917278647</v>
+        <v>0.003192487172782421</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.003528431057929993</v>
+        <v>0.02679160982370377</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.003177518025040627</v>
+        <v>0.001545518869534135</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0008929980103857815</v>
+        <v>0.01373695861548185</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0005684049101546407</v>
+        <v>0.00404196884483099</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.005799141712486744</v>
+        <v>0.01823518052697182</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.01320813875645399</v>
+        <v>0.06488766521215439</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0003337033558636904</v>
+        <v>0.001478932565078139</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.007693838328123093</v>
+        <v>0.01113766431808472</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.006521150004118681</v>
+        <v>0.04418439045548439</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.006584040820598602</v>
+        <v>0.09144884347915649</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.01010343059897423</v>
+        <v>0.008445840328931808</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0003733600024133921</v>
+        <v>0.03639519587159157</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.00116759177763015</v>
+        <v>0.05446391180157661</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.008815936744213104</v>
+        <v>0.014670729637146</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.00530930794775486</v>
+        <v>0.02161198481917381</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.003243394196033478</v>
+        <v>0.02126334607601166</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.006585897412151098</v>
+        <v>0.02006225101649761</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0006599151529371738</v>
+        <v>0.02598421834409237</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.005731214769184589</v>
+        <v>0.01037867181003094</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0007341436576098204</v>
+        <v>0.01314411964267492</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.00318459514528513</v>
+        <v>0.02635753154754639</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.002571107354015112</v>
+        <v>0.003915389068424702</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.002127313986420631</v>
+        <v>0.01242668647319078</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.006031826138496399</v>
+        <v>0.02233811654150486</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.008792264387011528</v>
+        <v>0.04708671197295189</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.001293137902393937</v>
+        <v>0.009769531898200512</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.009033365175127983</v>
+        <v>0.0156627893447876</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0007130755111575127</v>
+        <v>0.007936669513583183</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.001459125080145895</v>
+        <v>0.01108031440526247</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.00337718753144145</v>
+        <v>0.002569232136011124</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.001003636512905359</v>
+        <v>0.05869410932064056</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0009262855164706707</v>
+        <v>0.007963157258927822</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.001310235471464694</v>
+        <v>0.01502485666424036</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0009948206134140491</v>
+        <v>0.02060052193701267</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.003993221092969179</v>
+        <v>0.01690355874598026</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0009793840581551194</v>
+        <v>0.02509699389338493</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0001843007630668581</v>
+        <v>0.0218685083091259</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.003592126304283738</v>
+        <v>0.009886442683637142</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.001014704583212733</v>
+        <v>0.001422056462615728</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.001172739081084728</v>
+        <v>0.01342211849987507</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.004319521132856607</v>
+        <v>0.02038548700511456</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.003089906182140112</v>
+        <v>0.03707204759120941</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.001422884175553918</v>
+        <v>0.008451139554381371</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.004691152833402157</v>
+        <v>0.02154847607016563</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.005092812702059746</v>
+        <v>0.06571722030639648</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01775632239878178</v>
+        <v>0.06305637210607529</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.003616589121520519</v>
+        <v>0.004771136213093996</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.003748293966054916</v>
+        <v>0.006764085963368416</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.00125773111358285</v>
+        <v>9.095272980630398e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.003806994063779712</v>
+        <v>0.00692056305706501</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.005405740812420845</v>
+        <v>0.04023068025708199</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0004473218286875635</v>
+        <v>0.0106699513271451</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.004392821341753006</v>
+        <v>0.005708628334105015</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.001908714533783495</v>
+        <v>0.01531482581049204</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.003292085835710168</v>
+        <v>0.02050469256937504</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.003414360573515296</v>
+        <v>0.009375061839818954</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.0006595845334231853</v>
+        <v>0.00232895533554256</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.001589015475474298</v>
+        <v>0.01164269540458918</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.004035197664052248</v>
+        <v>0.005721396766602993</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.008208377286791801</v>
+        <v>0.05139253288507462</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.003356321947649121</v>
+        <v>0.03759973123669624</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.001708153868094087</v>
+        <v>0.02254746854305267</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.00433329539373517</v>
+        <v>0.00294792652130127</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.00665395287796855</v>
+        <v>0.05122779309749603</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.001208975445479155</v>
+        <v>0.003505985951051116</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.002855119528248906</v>
+        <v>0.0673273578286171</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.002523495815694332</v>
+        <v>0.04171488061547279</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.00448597501963377</v>
+        <v>0.01304329000413418</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.002168602310121059</v>
+        <v>0.02884932607412338</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.001790540758520365</v>
+        <v>0.01209484040737152</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.001868282910436392</v>
+        <v>0.05340932309627533</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01145441643893719</v>
+        <v>0.03727273270487785</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0026862439699471</v>
+        <v>0.007678430061787367</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.0003607650869525969</v>
+        <v>0.01802273094654083</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.002559324726462364</v>
+        <v>0.07960478961467743</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.001219025114551187</v>
+        <v>0.01001189462840557</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.000791651604231447</v>
+        <v>0.03737730905413628</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.009356183931231499</v>
+        <v>0.02253254875540733</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.001770670874975622</v>
+        <v>0.03106336481869221</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.007653066888451576</v>
+        <v>0.0009686225093901157</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.002402289770543575</v>
+        <v>0.02184227854013443</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.005477508064359426</v>
+        <v>0.004518754780292511</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.008362571708858013</v>
+        <v>0.009018683806061745</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.004611436277627945</v>
+        <v>0.003551442176103592</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0001280186697840691</v>
+        <v>0.01990342698991299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.002947924891486764</v>
+        <v>0.0006802146090194583</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03280545771121979</v>
+        <v>0.003272334579378366</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002339058555662632</v>
+        <v>1.585792051628232e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01778316311538219</v>
+        <v>0.003325699828565121</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005369465332478285</v>
+        <v>0.0007873543072491884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008615980856120586</v>
+        <v>0.0008512986823916435</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003224899526685476</v>
+        <v>0.001615505199879408</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002307881833985448</v>
+        <v>0.00139590771868825</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003419493557885289</v>
+        <v>0.0001726715418044478</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005836810916662216</v>
+        <v>0.0006135307485237718</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02403227612376213</v>
+        <v>0.0032750079408288</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008490533800795674</v>
+        <v>0.0005972021026536822</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01551007386296988</v>
+        <v>0.004692110233008862</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007310581393539906</v>
+        <v>0.00113637198228389</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01068428345024586</v>
+        <v>0.0006285935523919761</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002680481877177954</v>
+        <v>0.002038816688582301</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002534300787374377</v>
+        <v>4.402321064844728e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002960771089419723</v>
+        <v>0.0002036658115684986</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001720662694424391</v>
+        <v>0.000329766160575673</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00422517117112875</v>
+        <v>2.356587356189266e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001411990029737353</v>
+        <v>4.806074502994306e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004007472191005945</v>
+        <v>2.593658973637503e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005402926821261644</v>
+        <v>0.0004576633218675852</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002842095214873552</v>
+        <v>0.0007468179101124406</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003677321830764413</v>
+        <v>0.0002561943547334522</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004525172989815474</v>
+        <v>0.0008498161332681775</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003749377094209194</v>
+        <v>0.0007437057793140411</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.811585389077663e-05</v>
+        <v>0.0007151527097448707</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003152636345475912</v>
+        <v>0.0001854938454926014</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0002540461136959493</v>
+        <v>0.0004787779762409627</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0007168017327785492</v>
+        <v>7.223247666843235e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0005136645631864667</v>
+        <v>0.0004017619939986616</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001397314015775919</v>
+        <v>0.0007849992252886295</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001463894732296467</v>
+        <v>4.317241837270558e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001366973505355418</v>
+        <v>0.0003405541356187314</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.002288162242621183</v>
+        <v>0.0003693030157592148</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.002801521914079785</v>
+        <v>0.0004014130099676549</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.004472492728382349</v>
+        <v>0.0008869881858117878</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.00158388854470104</v>
+        <v>0.0005125451716594398</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.00127121212426573</v>
+        <v>0.0007337998831644654</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002117315074428916</v>
+        <v>0.0001519537763670087</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.003308319486677647</v>
+        <v>0.0007079977076500654</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0009100089082494378</v>
+        <v>0.0005991194630041718</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.002134380862116814</v>
+        <v>2.406546627753414e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003047912381589413</v>
+        <v>4.046786489197984e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002242505084723234</v>
+        <v>0.000191003578947857</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.02233587577939034</v>
+        <v>0.001898353104479611</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001584518468007445</v>
+        <v>0.0001007086539175361</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.004935343749821186</v>
+        <v>0.001923994743265212</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001041138544678688</v>
+        <v>0.002767193596810102</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002863808535039425</v>
+        <v>0.0006044674082659185</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0007845891523174942</v>
+        <v>5.358887574402615e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0007058927440084517</v>
+        <v>0.0002266840601805598</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004724040627479553</v>
+        <v>0.0002886973088607192</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001856108894571662</v>
+        <v>0.0005772972945123911</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.005292255431413651</v>
+        <v>2.827495336532593e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.005351375322788954</v>
+        <v>0.0002759293420240283</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.002630901988595724</v>
+        <v>0.000647274311631918</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.007143591064959764</v>
+        <v>0.0009796734666451812</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.003336219349876046</v>
+        <v>0.0003193395677953959</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.004599552601575851</v>
+        <v>0.0004821083857677877</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002445173216983676</v>
+        <v>0.001155238132923841</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002185064367949963</v>
+        <v>0.0005805939435958862</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.002481537638232112</v>
+        <v>0.0002339310594834387</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003600734518840909</v>
+        <v>0.0001642034767428413</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001909847953356802</v>
+        <v>1.385188443236984e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001761878607794642</v>
+        <v>0.0006487051723524928</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001871749525889754</v>
+        <v>8.77159764058888e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.002210650127381086</v>
+        <v>0.0003708981967065483</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0002760296047199517</v>
+        <v>0.000124016311019659</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001183290150947869</v>
+        <v>0.0003804096486419439</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001333657535724342</v>
+        <v>7.966908015077934e-06</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002444169018417597</v>
+        <v>3.813349758274853e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01171885244548321</v>
+        <v>0.001183530199341476</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.002618096070364118</v>
+        <v>0.0002730085689108819</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.004187427461147308</v>
+        <v>0.002012797631323338</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.00155063159763813</v>
+        <v>0.0007500616484321654</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002809145953506231</v>
+        <v>0.0006178821786306798</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.000430589250754565</v>
+        <v>0.0003526996297296137</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002388471271842718</v>
+        <v>0.0002869352174457163</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004109238274395466</v>
+        <v>0.0005347345140762627</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001579720992594957</v>
+        <v>2.379493707849178e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.005202739033848047</v>
+        <v>0.001005019992589951</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002743255812674761</v>
+        <v>7.006670057307929e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002251005731523037</v>
+        <v>0.001298265298828483</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0009048980427905917</v>
+        <v>9.538626181893051e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002049124101176858</v>
+        <v>2.983303056680597e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.001365044969134033</v>
+        <v>0.0001604787685209885</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0006197997718118131</v>
+        <v>0.0001031313731800765</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001849830383434892</v>
+        <v>0.0001836735173128545</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.003484366461634636</v>
+        <v>0.0004318004357628524</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0008852654136717319</v>
+        <v>0.0007288126507773995</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0006280867382884026</v>
+        <v>0.001028391299769282</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.004340421408414841</v>
+        <v>0.001797410193830729</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004940305836498737</v>
+        <v>0.0002730910782702267</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.002131478395313025</v>
+        <v>0.0003549234534148127</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.004592141602188349</v>
+        <v>0.0001610634644748643</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.005180567502975464</v>
+        <v>0.0004786949430126697</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0008280274923890829</v>
+        <v>0.0004635837394744158</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.001276464550755918</v>
+        <v>4.69835867988877e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.004638776183128357</v>
+        <v>0.001015549642033875</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002843111520633101</v>
+        <v>0.00016567058628425</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.00353429839015007</v>
+        <v>0.001410673256032169</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001024781842716038</v>
+        <v>0.0002416394272586331</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.002600279171019793</v>
+        <v>7.066718535497785e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001323213800787926</v>
+        <v>0.0002426535065751523</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001202184706926346</v>
+        <v>2.926763772848062e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001122735906392336</v>
+        <v>0.0002629954251460731</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.00188516650814563</v>
+        <v>0.0002168493228964508</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.004385742824524641</v>
+        <v>0.0008310906705446541</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001035754568874836</v>
+        <v>0.000265515292994678</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.009901490993797779</v>
+        <v>0.001150798052549362</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.003088183701038361</v>
+        <v>3.821769496425986e-07</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0009536295547150075</v>
+        <v>0.001342711504548788</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.002778710564598441</v>
+        <v>0.0005161702865734696</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.00130720972083509</v>
+        <v>0.001720919157378376</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0008019760134629905</v>
+        <v>0.0007335651898756623</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001512863789685071</v>
+        <v>0.0002620292361825705</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001409488962963223</v>
+        <v>0.0003666520933620632</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001324761775322258</v>
+        <v>1.762653118930757e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001096857362426817</v>
+        <v>0.0003846061590593308</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001801646081730723</v>
+        <v>5.093685831525363e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002773152198642492</v>
+        <v>0.0003988318494521081</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0003904622280970216</v>
+        <v>0.0005822516395710409</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001260719262063503</v>
+        <v>0.0007072306470945477</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.003092656377702951</v>
+        <v>0.001784203806892037</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.001378813525661826</v>
+        <v>3.769891918636858e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.415274113649502e-05</v>
+        <v>0.000117746923933737</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.004921239335089922</v>
+        <v>0.0001532518508611247</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0005155310500413179</v>
+        <v>0.0005768018309026957</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002045867266133428</v>
+        <v>0.0001981290988624096</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0004558535583782941</v>
+        <v>0.001031317748129368</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001308101462200284</v>
+        <v>8.779659401625395e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0004301772569306195</v>
+        <v>0.001936335931532085</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0002282868081238121</v>
+        <v>0.001385910203680396</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0003456661361269653</v>
+        <v>0.000619106343947351</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.003150530625134706</v>
+        <v>0.0006878427811898291</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.001665914664044976</v>
+        <v>0.0004296008846722543</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002012438140809536</v>
+        <v>0.001191376009956002</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0005577500560320914</v>
+        <v>9.289415902458131e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.002042885171249509</v>
+        <v>5.798290658276528e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0008264497737400234</v>
+        <v>7.680783892283216e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0004000484477728605</v>
+        <v>9.560642502037808e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0007521156221628189</v>
+        <v>0.0001562605466460809</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0002459913957864046</v>
+        <v>0.0004643319407477975</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.003452015342190862</v>
+        <v>0.001060353126376867</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001562107936479151</v>
+        <v>2.626332570798695e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.002519428497180343</v>
+        <v>0.001072156243026257</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.002340428531169891</v>
+        <v>0.0004461776115931571</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.008671900257468224</v>
+        <v>0.0003323944110888988</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.003593070432543755</v>
+        <v>0.0004722294688690454</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.005150143057107925</v>
+        <v>0.0002576175611466169</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0001081324589904398</v>
+        <v>0.0009088072692975402</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0008721661870367825</v>
+        <v>4.453899600775912e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.004473123699426651</v>
+        <v>0.001069235964678228</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.001679373672232032</v>
+        <v>7.599331729579717e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.003117513144388795</v>
+        <v>0.001488936017267406</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.001218748511746526</v>
+        <v>0.0001281608856515959</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.002276742132380605</v>
+        <v>7.965630356920883e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.00206920993514359</v>
+        <v>0.0002700428885873407</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0007873887079767883</v>
+        <v>0.0002067636960418895</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.002069254405796528</v>
+        <v>0.0003097996523138136</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0006266703130677342</v>
+        <v>0.0001218921097461134</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.00257001630961895</v>
+        <v>0.0004695154202636331</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.00186573714017868</v>
+        <v>0.0006091510877013206</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.002760299015790224</v>
+        <v>0.000765143777243793</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0002113505179295316</v>
+        <v>0.0004025666858069599</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0008936415542848408</v>
+        <v>0.0007159117376431823</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0008738380274735391</v>
+        <v>0.0004661449347622693</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.002080164849758148</v>
+        <v>0.0004780225572176278</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.001076946035027504</v>
+        <v>0.0005095580127090216</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0008680990431457758</v>
+        <v>0.0007469734409824014</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.003548114560544491</v>
+        <v>0.001611227402463555</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.002171684987843037</v>
+        <v>9.388398029841483e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.00147516094148159</v>
+        <v>0.001364050433039665</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.00192985450848937</v>
+        <v>0.0007005073712207377</v>
       </c>
       <c r="FU4" t="n">
-        <v>9.682247036835179e-05</v>
+        <v>0.001226059743203223</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.001863454934209585</v>
+        <v>0.0001350153615931049</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0001816281001083553</v>
+        <v>0.0008965951856225729</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.001220178324729204</v>
+        <v>0.00117102253716439</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.004306875634938478</v>
+        <v>0.0005680334288626909</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0008154776296578348</v>
+        <v>0.0001624386932235211</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001841571065597236</v>
+        <v>7.726781768724322e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>8.12058278825134e-05</v>
+        <v>0.001255577313713729</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.004472238942980766</v>
+        <v>0.0011307013919577</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.002505081938579679</v>
+        <v>0.0001988203730434179</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.01163824275135994</v>
+        <v>0.0008236514986492693</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.001436441205441952</v>
+        <v>0.0005887323059141636</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.00143499777186662</v>
+        <v>0.000400777324102819</v>
       </c>
     </row>
     <row r="5">
@@ -3275,1709 +3275,1709 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5.210547548983868e-09</v>
+        <v>1.823408446455232e-08</v>
       </c>
       <c r="B6" t="n">
-        <v>5.802372982088855e-08</v>
+        <v>7.393487067020033e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.54993279216842e-09</v>
+        <v>1.051079046021641e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.998607453098884e-08</v>
+        <v>2.006341048854665e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.423499629282787e-08</v>
+        <v>1.632530022277479e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.918236567481472e-09</v>
+        <v>1.795516979541389e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.083317702210707e-08</v>
+        <v>9.623630781163683e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>7.498470733224849e-10</v>
+        <v>2.170972512871572e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>3.08601943999065e-09</v>
+        <v>5.744849485012082e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.809808303221416e-08</v>
+        <v>8.755502101109869e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.734310993763756e-08</v>
+        <v>8.961799835560669e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.926594605019318e-09</v>
+        <v>1.712718855628736e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.230234378927889e-08</v>
+        <v>3.384391789040819e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.262801584469344e-08</v>
+        <v>3.224234390586389e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.653098813392262e-08</v>
+        <v>1.871733346092697e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.712141894927299e-08</v>
+        <v>4.15316758761719e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.408365595840678e-08</v>
+        <v>1.421972228854429e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>8.663825212806842e-10</v>
+        <v>1.493024548437916e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>9.959882696364275e-09</v>
+        <v>2.600046844491999e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>9.047495197478383e-09</v>
+        <v>4.022636446165961e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>8.937868223313217e-09</v>
+        <v>5.637732503060988e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.294419569423781e-09</v>
+        <v>6.484854875310475e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>1.516087522190901e-08</v>
+        <v>8.256730410494129e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.020812057106468e-08</v>
+        <v>7.577788174728539e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.121901670510852e-08</v>
+        <v>1.819105044376101e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.505796541958262e-09</v>
+        <v>8.143045349129352e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.324232190569319e-08</v>
+        <v>7.697606108081345e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.166951393993259e-10</v>
+        <v>2.993739478540647e-09</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.386688345903167e-09</v>
+        <v>1.332835619649586e-09</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.979936881113531e-09</v>
+        <v>6.087538029220241e-09</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.268521820918522e-08</v>
+        <v>2.455434255921318e-08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.503611990472109e-08</v>
+        <v>2.488700445724135e-08</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.679572729315851e-09</v>
+        <v>2.659934494886329e-08</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.25355694900054e-09</v>
+        <v>4.751059101693045e-09</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.543981439539493e-09</v>
+        <v>1.997221588112552e-08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.438432649716106e-09</v>
+        <v>2.573754098733616e-09</v>
       </c>
       <c r="AK6" t="n">
-        <v>7.989385153450712e-09</v>
+        <v>2.580868851964624e-10</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.313552822068687e-08</v>
+        <v>1.472592003892714e-08</v>
       </c>
       <c r="AM6" t="n">
-        <v>9.05348906954373e-10</v>
+        <v>1.02842383498114e-08</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.647136897517612e-09</v>
+        <v>8.698100018023069e-09</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.969197332447493e-09</v>
+        <v>5.009122006072175e-10</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.875801623034249e-09</v>
+        <v>1.011345940327146e-08</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.071475175251635e-08</v>
+        <v>1.102712765543856e-08</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.790921798696445e-09</v>
+        <v>3.962380645816665e-09</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.415861867978492e-09</v>
+        <v>1.147794082001496e-10</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.440550149809042e-09</v>
+        <v>9.343346096812866e-10</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.386116276260509e-08</v>
+        <v>5.879144637788158e-08</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.544170094713309e-09</v>
+        <v>1.073950262053813e-08</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.106065970039708e-08</v>
+        <v>1.123780091205617e-08</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.789424299493476e-09</v>
+        <v>2.942224952562356e-08</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.059219734145245e-08</v>
+        <v>2.333647053376353e-08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.538527053123744e-09</v>
+        <v>3.28156124496104e-09</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.033288369953425e-09</v>
+        <v>1.105774138920879e-08</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.716413322583321e-08</v>
+        <v>5.015993842505395e-09</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.062005594576476e-09</v>
+        <v>5.142060555130001e-09</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.083286153644394e-09</v>
+        <v>1.31391502122824e-08</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.919987249887072e-09</v>
+        <v>1.338379806981038e-08</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.33595076615245e-09</v>
+        <v>8.071624257866006e-09</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.51714791232871e-08</v>
+        <v>2.485176686661816e-08</v>
       </c>
       <c r="BH6" t="n">
-        <v>1.139850169806778e-08</v>
+        <v>1.34183653077713e-09</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.641118612700666e-08</v>
+        <v>3.217879296357751e-10</v>
       </c>
       <c r="BJ6" t="n">
-        <v>3.567212303323686e-08</v>
+        <v>1.244610459139039e-08</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.784888764040261e-09</v>
+        <v>6.125078222396496e-09</v>
       </c>
       <c r="BL6" t="n">
-        <v>2.375099672491388e-09</v>
+        <v>2.860390146963709e-09</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.611921846000897e-10</v>
+        <v>8.594547296070232e-09</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.777006097825051e-08</v>
+        <v>2.916091812465993e-09</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.94880722459834e-09</v>
+        <v>4.968674804928241e-09</v>
       </c>
       <c r="BP6" t="n">
-        <v>7.082157083004859e-09</v>
+        <v>2.499538709344051e-08</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.193321494014526e-09</v>
+        <v>6.731963431150234e-09</v>
       </c>
       <c r="BR6" t="n">
-        <v>9.26967125280953e-09</v>
+        <v>6.261048568489969e-09</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.665107690091872e-09</v>
+        <v>9.325185956754467e-09</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.183584838088564e-09</v>
+        <v>1.02473540763981e-09</v>
       </c>
       <c r="BU6" t="n">
-        <v>8.986672739297319e-09</v>
+        <v>3.479429411257229e-09</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.799305771044146e-08</v>
+        <v>3.855009822473221e-08</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.107118532052482e-09</v>
+        <v>7.518911715465038e-09</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.921306314045523e-08</v>
+        <v>1.026525087155505e-09</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.13740847851318e-08</v>
+        <v>8.270747420269231e-10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.839856156315989e-09</v>
+        <v>1.633367396891572e-08</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.186656284346554e-08</v>
+        <v>1.558908202525799e-08</v>
       </c>
       <c r="CB6" t="n">
-        <v>7.597092732680721e-09</v>
+        <v>7.710309724018316e-09</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.474895938713416e-08</v>
+        <v>9.395188627081552e-09</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.797009539065812e-10</v>
+        <v>4.15698897526795e-09</v>
       </c>
       <c r="CE6" t="n">
-        <v>9.341610152091562e-09</v>
+        <v>2.500839180186176e-08</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.150306960795433e-08</v>
+        <v>9.449339088973829e-10</v>
       </c>
       <c r="CG6" t="n">
-        <v>1.155879658654158e-08</v>
+        <v>5.545535586293227e-09</v>
       </c>
       <c r="CH6" t="n">
-        <v>5.133945712998411e-09</v>
+        <v>8.704084564215009e-09</v>
       </c>
       <c r="CI6" t="n">
-        <v>3.017175120856308e-10</v>
+        <v>8.26969870360017e-09</v>
       </c>
       <c r="CJ6" t="n">
-        <v>9.485408014597851e-09</v>
+        <v>3.467581999316849e-09</v>
       </c>
       <c r="CK6" t="n">
-        <v>4.404383524558853e-09</v>
+        <v>5.400802916000202e-09</v>
       </c>
       <c r="CL6" t="n">
-        <v>8.633700865345872e-09</v>
+        <v>1.29149024807873e-09</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.861247156398349e-08</v>
+        <v>2.55990961761654e-08</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.079797584679909e-08</v>
+        <v>4.092119709753206e-08</v>
       </c>
       <c r="CO6" t="n">
-        <v>2.170941648671487e-09</v>
+        <v>2.326893522308637e-08</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.034833990194329e-08</v>
+        <v>1.621654144301488e-09</v>
       </c>
       <c r="CQ6" t="n">
-        <v>7.817980041124883e-09</v>
+        <v>1.585793540925806e-08</v>
       </c>
       <c r="CR6" t="n">
-        <v>4.935009734197138e-09</v>
+        <v>1.71741056931296e-08</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.111892977689877e-08</v>
+        <v>1.462510201832856e-08</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.224215561203891e-08</v>
+        <v>5.952958126442809e-09</v>
       </c>
       <c r="CU6" t="n">
-        <v>9.377705723068175e-09</v>
+        <v>2.689361844332439e-09</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.131490678929481e-09</v>
+        <v>2.327208203922737e-09</v>
       </c>
       <c r="CW6" t="n">
-        <v>9.1886072084435e-09</v>
+        <v>2.350619077162719e-08</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.029000973318261e-08</v>
+        <v>2.447911207070774e-09</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.82079791244405e-08</v>
+        <v>7.438383242686086e-09</v>
       </c>
       <c r="CZ6" t="n">
-        <v>7.286057979172256e-09</v>
+        <v>1.069455723978763e-08</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.190692766079749e-10</v>
+        <v>7.814341174139372e-09</v>
       </c>
       <c r="DB6" t="n">
-        <v>7.281562020011734e-09</v>
+        <v>6.568813937235518e-09</v>
       </c>
       <c r="DC6" t="n">
-        <v>5.951850123864233e-09</v>
+        <v>3.874721876684362e-09</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.045341560678708e-09</v>
+        <v>3.67769215081637e-09</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.489770706797344e-08</v>
+        <v>1.090945289661249e-08</v>
       </c>
       <c r="DF6" t="n">
-        <v>6.10747230567199e-09</v>
+        <v>5.47133183204096e-09</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.839761454291988e-09</v>
+        <v>3.322863761923145e-09</v>
       </c>
       <c r="DH6" t="n">
-        <v>6.515026029774162e-08</v>
+        <v>7.422699788151021e-09</v>
       </c>
       <c r="DI6" t="n">
-        <v>3.981282148401988e-08</v>
+        <v>7.84894105265721e-09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>5.094277000239344e-09</v>
+        <v>2.898646833671137e-08</v>
       </c>
       <c r="DK6" t="n">
-        <v>2.454792102923875e-08</v>
+        <v>8.154219521827599e-09</v>
       </c>
       <c r="DL6" t="n">
-        <v>3.211643218037352e-08</v>
+        <v>1.482294109678151e-08</v>
       </c>
       <c r="DM6" t="n">
-        <v>4.166506695213457e-09</v>
+        <v>1.078084022054782e-08</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.496844426185362e-09</v>
+        <v>3.650345581363013e-09</v>
       </c>
       <c r="DO6" t="n">
-        <v>7.004810509414483e-09</v>
+        <v>1.564383467211883e-08</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.295954454860748e-08</v>
+        <v>6.205258529234925e-09</v>
       </c>
       <c r="DQ6" t="n">
-        <v>9.856545801767425e-09</v>
+        <v>6.175099542815587e-09</v>
       </c>
       <c r="DR6" t="n">
-        <v>1.266288851553554e-08</v>
+        <v>7.739956231489487e-09</v>
       </c>
       <c r="DS6" t="n">
-        <v>9.492366892516202e-09</v>
+        <v>6.072573555115923e-09</v>
       </c>
       <c r="DT6" t="n">
-        <v>4.921309582073263e-09</v>
+        <v>1.333004018277961e-08</v>
       </c>
       <c r="DU6" t="n">
-        <v>1.317167486192261e-10</v>
+        <v>1.689534290250094e-09</v>
       </c>
       <c r="DV6" t="n">
-        <v>9.694065994381162e-09</v>
+        <v>5.143854231448586e-09</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.031081969278148e-09</v>
+        <v>2.439818569399677e-09</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.34058861789299e-08</v>
+        <v>1.403997718085748e-08</v>
       </c>
       <c r="DY6" t="n">
-        <v>1.154959061722138e-08</v>
+        <v>4.397000541445095e-09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.161351429057049e-09</v>
+        <v>1.248068315362616e-09</v>
       </c>
       <c r="EA6" t="n">
-        <v>2.75865605914305e-08</v>
+        <v>2.749706951021835e-08</v>
       </c>
       <c r="EB6" t="n">
-        <v>5.671711544863456e-09</v>
+        <v>6.556355014453175e-09</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.87350535085784e-09</v>
+        <v>1.237735691717035e-09</v>
       </c>
       <c r="ED6" t="n">
-        <v>1.027224172389651e-08</v>
+        <v>2.01471443972423e-08</v>
       </c>
       <c r="EE6" t="n">
-        <v>7.887374309234474e-09</v>
+        <v>2.171462476496799e-08</v>
       </c>
       <c r="EF6" t="n">
-        <v>2.907915241934234e-09</v>
+        <v>6.111044115186814e-09</v>
       </c>
       <c r="EG6" t="n">
-        <v>6.589939260948086e-09</v>
+        <v>5.527406088390308e-09</v>
       </c>
       <c r="EH6" t="n">
-        <v>1.127109960918915e-08</v>
+        <v>8.031638465411106e-09</v>
       </c>
       <c r="EI6" t="n">
-        <v>1.547660843925769e-08</v>
+        <v>6.673311681026917e-09</v>
       </c>
       <c r="EJ6" t="n">
-        <v>9.831644831592712e-09</v>
+        <v>6.804993901710077e-09</v>
       </c>
       <c r="EK6" t="n">
-        <v>1.195238241713525e-09</v>
+        <v>8.007118523778445e-09</v>
       </c>
       <c r="EL6" t="n">
-        <v>1.378825231768133e-08</v>
+        <v>7.016516256896921e-09</v>
       </c>
       <c r="EM6" t="n">
-        <v>5.733744146141362e-09</v>
+        <v>4.775504436338451e-09</v>
       </c>
       <c r="EN6" t="n">
-        <v>4.304271605803933e-09</v>
+        <v>1.1008662426093e-08</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.569887553287685e-09</v>
+        <v>4.15121448327227e-09</v>
       </c>
       <c r="EP6" t="n">
-        <v>2.429879408794022e-09</v>
+        <v>1.823965334324384e-08</v>
       </c>
       <c r="EQ6" t="n">
-        <v>8.893137781740279e-09</v>
+        <v>3.708155338344454e-09</v>
       </c>
       <c r="ER6" t="n">
-        <v>7.735726725854875e-09</v>
+        <v>6.44764019952504e-10</v>
       </c>
       <c r="ES6" t="n">
-        <v>3.842746920668105e-08</v>
+        <v>1.007055860924311e-08</v>
       </c>
       <c r="ET6" t="n">
-        <v>6.438521715779189e-09</v>
+        <v>7.825582848397516e-09</v>
       </c>
       <c r="EU6" t="n">
-        <v>7.721804529126075e-09</v>
+        <v>1.352085443606654e-09</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.105979841042881e-08</v>
+        <v>4.164716127519341e-09</v>
       </c>
       <c r="EW6" t="n">
-        <v>2.411434385507505e-09</v>
+        <v>7.891196140974444e-09</v>
       </c>
       <c r="EX6" t="n">
-        <v>2.756989969654455e-09</v>
+        <v>3.929624625698125e-09</v>
       </c>
       <c r="EY6" t="n">
-        <v>9.463458461311802e-09</v>
+        <v>2.611027838383961e-08</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1.137654326299753e-08</v>
+        <v>1.741693234080799e-09</v>
       </c>
       <c r="FA6" t="n">
-        <v>1.690347950500382e-08</v>
+        <v>6.147147679769205e-09</v>
       </c>
       <c r="FB6" t="n">
-        <v>4.030286770984048e-09</v>
+        <v>4.931591135459712e-09</v>
       </c>
       <c r="FC6" t="n">
-        <v>8.984407107170966e-10</v>
+        <v>8.861469780185871e-09</v>
       </c>
       <c r="FD6" t="n">
-        <v>9.119966115633815e-09</v>
+        <v>4.817364285258918e-10</v>
       </c>
       <c r="FE6" t="n">
-        <v>6.06449690465638e-09</v>
+        <v>5.252028589808333e-09</v>
       </c>
       <c r="FF6" t="n">
-        <v>1.008190331219794e-08</v>
+        <v>6.367549598707001e-09</v>
       </c>
       <c r="FG6" t="n">
-        <v>2.847690305785022e-09</v>
+        <v>6.044335698618397e-09</v>
       </c>
       <c r="FH6" t="n">
-        <v>5.705762973207129e-09</v>
+        <v>2.700740298067217e-09</v>
       </c>
       <c r="FI6" t="n">
-        <v>1.407185123980526e-08</v>
+        <v>3.058308273296007e-09</v>
       </c>
       <c r="FJ6" t="n">
-        <v>3.102013579336926e-08</v>
+        <v>5.078055309581941e-09</v>
       </c>
       <c r="FK6" t="n">
-        <v>3.642760315614169e-09</v>
+        <v>6.809524499828967e-09</v>
       </c>
       <c r="FL6" t="n">
-        <v>2.350430294839612e-09</v>
+        <v>2.313999658554167e-09</v>
       </c>
       <c r="FM6" t="n">
-        <v>1.562714402325582e-08</v>
+        <v>2.887913463922587e-09</v>
       </c>
       <c r="FN6" t="n">
-        <v>2.993397751893667e-09</v>
+        <v>1.53400243618762e-08</v>
       </c>
       <c r="FO6" t="n">
-        <v>1.062798560269584e-08</v>
+        <v>1.909241120756633e-08</v>
       </c>
       <c r="FP6" t="n">
-        <v>1.423212303564014e-08</v>
+        <v>1.444801966954401e-08</v>
       </c>
       <c r="FQ6" t="n">
-        <v>3.869365383657453e-10</v>
+        <v>4.607905168541038e-09</v>
       </c>
       <c r="FR6" t="n">
-        <v>7.273794455642246e-09</v>
+        <v>1.136904081988632e-08</v>
       </c>
       <c r="FS6" t="n">
-        <v>3.643880086556806e-09</v>
+        <v>1.489770884433028e-08</v>
       </c>
       <c r="FT6" t="n">
-        <v>2.256900621944169e-08</v>
+        <v>1.679667427367804e-08</v>
       </c>
       <c r="FU6" t="n">
-        <v>3.121999547772702e-09</v>
+        <v>8.579430499366936e-09</v>
       </c>
       <c r="FV6" t="n">
-        <v>6.227109938805597e-09</v>
+        <v>1.055711162933903e-08</v>
       </c>
       <c r="FW6" t="n">
-        <v>9.707447290452365e-09</v>
+        <v>9.121379207499558e-10</v>
       </c>
       <c r="FX6" t="n">
-        <v>8.467862855354724e-09</v>
+        <v>8.08906330806991e-10</v>
       </c>
       <c r="FY6" t="n">
-        <v>1.491718748525273e-08</v>
+        <v>1.020541873231195e-09</v>
       </c>
       <c r="FZ6" t="n">
-        <v>3.406364967872832e-09</v>
+        <v>8.208989044078407e-09</v>
       </c>
       <c r="GA6" t="n">
-        <v>7.273037727628662e-10</v>
+        <v>2.948852717565842e-09</v>
       </c>
       <c r="GB6" t="n">
-        <v>3.781955193460362e-09</v>
+        <v>7.574573857027644e-09</v>
       </c>
       <c r="GC6" t="n">
-        <v>9.785459553768305e-09</v>
+        <v>1.011182693133605e-09</v>
       </c>
       <c r="GD6" t="n">
-        <v>3.714955898459493e-09</v>
+        <v>1.875280197793927e-08</v>
       </c>
       <c r="GE6" t="n">
-        <v>4.240694906343379e-08</v>
+        <v>2.425410627893143e-08</v>
       </c>
       <c r="GF6" t="n">
-        <v>6.287341758337561e-09</v>
+        <v>1.746985001105372e-09</v>
       </c>
       <c r="GG6" t="n">
-        <v>5.146586712356793e-09</v>
+        <v>1.085592682414926e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001486206543631852</v>
+        <v>0.0005846014828421175</v>
       </c>
       <c r="B7" t="n">
-        <v>0.006807019002735615</v>
+        <v>0.002517241751775146</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002512932696845382</v>
+        <v>0.000177958223503083</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003299443749710917</v>
+        <v>0.0001191696792375296</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002598739229142666</v>
+        <v>0.0008132895454764366</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004174555186182261</v>
+        <v>0.001475965138524771</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0004290640936233103</v>
+        <v>9.246352419722825e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002386514679528773</v>
+        <v>0.001044956617988646</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001663442817516625</v>
+        <v>0.0001933847524924204</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001777530880644917</v>
+        <v>0.0003321197291370481</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004243178758770227</v>
+        <v>0.003875768277794123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007089645368978381</v>
+        <v>7.772148819640279e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00432716216892004</v>
+        <v>0.001034079701639712</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001847339444793761</v>
+        <v>0.001644548261538148</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005300820805132389</v>
+        <v>0.001513035967946053</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009573474526405334</v>
+        <v>0.0002600203733891249</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001301054609939456</v>
+        <v>0.0001791009271983057</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002069722395390272</v>
+        <v>0.0006432052468881011</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004604569985531271</v>
+        <v>7.375748100457713e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00141101295594126</v>
+        <v>0.0002782000228762627</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002132708759745583</v>
+        <v>9.997739107348025e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0006925164489075541</v>
+        <v>0.0005474502104334533</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000555757840629667</v>
+        <v>0.0007078704074956477</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00019493953732308</v>
+        <v>0.0002509043843019754</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0005883801495656371</v>
+        <v>0.0002421153767500073</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.937269841320813e-05</v>
+        <v>0.0007541550439782441</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.000430832093115896</v>
+        <v>0.000111481494968757</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002611594391055405</v>
+        <v>0.0005567416083067656</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001397303771227598</v>
+        <v>0.0001801180187612772</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001262026344193146</v>
+        <v>5.464691639645025e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001006776466965675</v>
+        <v>0.0003470479568932205</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0004305829352233559</v>
+        <v>0.0009491078089922667</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001763437467161566</v>
+        <v>0.0004480210191104561</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.001079385634511709</v>
+        <v>0.0004411917761899531</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0002167597704101354</v>
+        <v>0.001616946305148304</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0002012031472986564</v>
+        <v>0.0001366675569443032</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0008641184540465474</v>
+        <v>0.0001186036024591886</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0008798527996987104</v>
+        <v>1.660950147197582e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.410875357687473e-05</v>
+        <v>0.0002812101738527417</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001676543906796724</v>
+        <v>0.0001521801750641316</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0002108685148414224</v>
+        <v>0.0003913312975782901</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.00124497280921787</v>
+        <v>0.000142235541716218</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0007808590889908373</v>
+        <v>0.0001376714644720778</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0002501400304026902</v>
+        <v>0.0009737501968629658</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0007308569038286805</v>
+        <v>5.107068864163011e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.001535324612632394</v>
+        <v>0.0003010525251738727</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.00634440965950489</v>
+        <v>0.00331419100984931</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0003506412031129003</v>
+        <v>4.461672506295145e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0005873377085663378</v>
+        <v>0.000109459477243945</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002039849292486906</v>
+        <v>0.001327454810962081</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001674337196163833</v>
+        <v>0.00126261415425688</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0003751165349967778</v>
+        <v>2.051999035757035e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001535506569780409</v>
+        <v>7.327440107474104e-05</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0008918148232623935</v>
+        <v>8.398218778893352e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.001129436073824763</v>
+        <v>8.095632074400783e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0007006471860222518</v>
+        <v>7.255509262904525e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.001646883436478674</v>
+        <v>0.0002004516427405179</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001298539573326707</v>
+        <v>0.0002152424422092736</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.002668994013220072</v>
+        <v>0.0001180690305773169</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002067905850708485</v>
+        <v>2.679259341675788e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0004367750661913306</v>
+        <v>9.837503603193909e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001966805895790458</v>
+        <v>0.001026827725581825</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0001161164400400594</v>
+        <v>0.0002429959131404757</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.000218068526010029</v>
+        <v>0.0001203646534122527</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.001853838213719428</v>
+        <v>0.001100689172744751</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0004969349829480052</v>
+        <v>8.881120447767898e-05</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.002724048681557178</v>
+        <v>0.0004931957228109241</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.002013929421082139</v>
+        <v>0.0009995839791372418</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0001856461021816358</v>
+        <v>0.0001844535727286711</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001147095812484622</v>
+        <v>0.0006314876955002546</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.000813815335277468</v>
+        <v>0.0006776803056709468</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.486049435101449e-05</v>
+        <v>7.572134200017899e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0006726866122335196</v>
+        <v>4.320420703152195e-05</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.002578734187409282</v>
+        <v>0.001916418899782002</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0002683346101548523</v>
+        <v>7.913698209449649e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>8.124842133838683e-05</v>
+        <v>0.000809761113487184</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003565559745766222</v>
+        <v>0.0005174580146558583</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0003159016487188637</v>
+        <v>0.0005665702046826482</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.001031353953294456</v>
+        <v>0.0004034315643366426</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0009362638229504228</v>
+        <v>0.0003923822077922523</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0005874565104022622</v>
+        <v>8.277199958683923e-05</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0002944862062577158</v>
+        <v>0.0003552294801920652</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001377713633701205</v>
+        <v>0.0007730837678536773</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0006947301444597542</v>
+        <v>3.205061511835083e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0008735416340641677</v>
+        <v>0.0002057974052149802</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004519018693827093</v>
+        <v>0.0001594519562786445</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0006747083971276879</v>
+        <v>0.0004850018885917962</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0003125695511698723</v>
+        <v>0.0001221835991600528</v>
       </c>
       <c r="CK7" t="n">
-        <v>6.590811972273514e-05</v>
+        <v>7.272438961081207e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0003595353045966476</v>
+        <v>2.668128763616551e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.001260703429579735</v>
+        <v>2.668710658326745e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001268660300411284</v>
+        <v>0.001710333046503365</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0006375177763402462</v>
+        <v>0.0004918693448416889</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0009303528349846601</v>
+        <v>0.0008262231713160872</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0005611253436654806</v>
+        <v>0.0001296965929213911</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.000484598393086344</v>
+        <v>0.0002743260702118278</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0003095152787864208</v>
+        <v>8.491930202580988e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0001945199619513005</v>
+        <v>0.0002350443392060697</v>
       </c>
       <c r="CU7" t="n">
-        <v>3.97203111788258e-05</v>
+        <v>0.0001088851058739237</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0001566081191413105</v>
+        <v>0.0001687853946350515</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0009605704690329731</v>
+        <v>0.0007065664976835251</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0007322282181121409</v>
+        <v>8.616436389274895e-06</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.001256527495570481</v>
+        <v>0.0003230849979445338</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0002341285144211724</v>
+        <v>2.291624696226791e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0007267237524501979</v>
+        <v>0.0004646754823625088</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0004242720897309482</v>
+        <v>5.105022864881903e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0003687622374854982</v>
+        <v>0.0001319461880484596</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0002518376568332314</v>
+        <v>0.0001257915573660284</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001216539647430182</v>
+        <v>0.0006447959458455443</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.002867399016395211</v>
+        <v>0.0004557715728878975</v>
       </c>
       <c r="DG7" t="n">
-        <v>7.630696200067177e-05</v>
+        <v>0.0005919536342844367</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001321608549915254</v>
+        <v>0.000522043090313673</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0004593129269778728</v>
+        <v>0.0006258063367567956</v>
       </c>
       <c r="DJ7" t="n">
-        <v>8.421570237260312e-05</v>
+        <v>0.0007987429271452129</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.001881011528894305</v>
+        <v>0.0003469035436864942</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0008308360120281577</v>
+        <v>0.0003946571378037333</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0003063533222302794</v>
+        <v>1.864598016254604e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.001199662219733</v>
+        <v>1.531967427581549e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0009078161092475057</v>
+        <v>0.0004362607432994992</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0008218484581448138</v>
+        <v>0.0002896625956054777</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0013337975833565</v>
+        <v>0.0007389416568912566</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0003271194873377681</v>
+        <v>9.37789591262117e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0006991417612880468</v>
+        <v>1.921556759043597e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>4.245087620802224e-05</v>
+        <v>0.0001289771898882464</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.000282284920103848</v>
+        <v>0.0009954986162483692</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0007586220162920654</v>
+        <v>1.952488673850894e-05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.000219780340557918</v>
+        <v>0.0002393424510955811</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0002560645225457847</v>
+        <v>0.0008828059653751552</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.001532336696982384</v>
+        <v>0.0002083730360027403</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0003536267904564738</v>
+        <v>0.0002746184763964266</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0005327914841473103</v>
+        <v>0.0005795100005343556</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0002885856374632567</v>
+        <v>0.0004528756253421307</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004334144468884915</v>
+        <v>0.0001307789643760771</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0002563072193879634</v>
+        <v>0.0005626374040730298</v>
       </c>
       <c r="EE7" t="n">
-        <v>6.512268009828404e-05</v>
+        <v>0.000910398259293288</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0004864013753831387</v>
+        <v>0.0004965534317307174</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0002018053928622976</v>
+        <v>0.00015521481691394</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001234784722328186</v>
+        <v>0.0001669426128501073</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0006295585772022605</v>
+        <v>0.0001007109676720574</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001248709304491058</v>
+        <v>0.0003164282243233174</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0004522643575910479</v>
+        <v>0.0005567314801737666</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0007641494157724082</v>
+        <v>6.983698403928429e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0002748067199718207</v>
+        <v>0.0003563429636415094</v>
       </c>
       <c r="EN7" t="n">
-        <v>5.543325823964551e-05</v>
+        <v>0.0001241731079062447</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001041163457557559</v>
+        <v>0.0001310873340116814</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0004199910908937454</v>
+        <v>0.0001163887427537702</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0003366875753272325</v>
+        <v>0.00014034632476978</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0007409265381284058</v>
+        <v>0.0002439071395201609</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0004729856445919722</v>
+        <v>0.0009131192928180099</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.00174214260187</v>
+        <v>0.0003059000009670854</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0003841374709736556</v>
+        <v>0.0004428372485563159</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0008063084678724408</v>
+        <v>0.0002792385639622808</v>
       </c>
       <c r="EW7" t="n">
-        <v>7.342823664657772e-06</v>
+        <v>0.0002437003859085962</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0002624844200909138</v>
+        <v>0.0002117330877808854</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0008736063027754426</v>
+        <v>0.0009516095742583275</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0004502944648265839</v>
+        <v>4.929975148115773e-06</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0008884831331670284</v>
+        <v>0.0003248094581067562</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0003377297834958881</v>
+        <v>4.932026058668271e-05</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0007163019618019462</v>
+        <v>0.0004696913820225745</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0005207597278058529</v>
+        <v>0.0001268519263248891</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.754664845066145e-05</v>
+        <v>8.159563003573567e-05</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0004335657577030361</v>
+        <v>0.0001775743294274434</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0007240570848807693</v>
+        <v>0.0003012408851645887</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.001006703008897603</v>
+        <v>0.0003421655856072903</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0007790733361616731</v>
+        <v>0.0001669202465564013</v>
       </c>
       <c r="FJ7" t="n">
-        <v>7.099981303326786e-05</v>
+        <v>0.0008313420112244785</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0001335612614639103</v>
+        <v>0.000364586419891566</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0001100831068470143</v>
+        <v>0.0002541200374253094</v>
       </c>
       <c r="FM7" t="n">
-        <v>6.191762804519385e-05</v>
+        <v>0.0004542214446701109</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0001263676676899195</v>
+        <v>0.0009692955063655972</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.000204540861886926</v>
+        <v>0.0003655819455161691</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0008271257393062115</v>
+        <v>6.478765862993896e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.00050924759125337</v>
+        <v>0.0002489289618097246</v>
       </c>
       <c r="FR7" t="n">
-        <v>6.275425403146073e-05</v>
+        <v>0.0006365741137415171</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.000828842050395906</v>
+        <v>0.0008116680546663702</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.003315428737550974</v>
+        <v>0.001000477815978229</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0007829103269614279</v>
+        <v>3.657814886537381e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0002227310906164348</v>
+        <v>0.0002158125716960058</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0009022242156788707</v>
+        <v>0.0005202368483878672</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0001623961288714781</v>
+        <v>0.0002433355257380754</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0006421832949854434</v>
+        <v>0.0004198919050395489</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001575912465341389</v>
+        <v>0.0003265315317548811</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0005455674836412072</v>
+        <v>0.0005198063445277512</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001409750548191369</v>
+        <v>0.0004462249344214797</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0002175473346142098</v>
+        <v>0.0007132446044124663</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0007559068617410958</v>
+        <v>0.000351337599568069</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.002105932682752609</v>
+        <v>1.428911036782665e-05</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.001548439380712807</v>
+        <v>0.0003680595546029508</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0004666115564759821</v>
+        <v>0.000703719793818891</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.01698906719684601</v>
+        <v>0.01936583034694195</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01356478314846754</v>
+        <v>0.001492100884206593</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0270003080368042</v>
+        <v>0.05129526555538177</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03953869640827179</v>
+        <v>0.07193666696548462</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00115719367749989</v>
+        <v>0.01976937800645828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004733632784336805</v>
+        <v>0.01144274976104498</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006126309745013714</v>
+        <v>0.02278864197432995</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01134235691279173</v>
+        <v>0.02359367534518242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006805885583162308</v>
+        <v>0.003981523215770721</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02183341048657894</v>
+        <v>0.01001280918717384</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01051208563148975</v>
+        <v>0.009305559098720551</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02271414175629616</v>
+        <v>0.04427734762430191</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03426921740174294</v>
+        <v>0.07670959830284119</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01392492651939392</v>
+        <v>0.0123517569154501</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00221268436871469</v>
+        <v>0.009561518207192421</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006741880904883146</v>
+        <v>0.01369793247431517</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01497939229011536</v>
+        <v>0.04509151354432106</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004127758089452982</v>
+        <v>0.00679912930354476</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009752728976309299</v>
+        <v>0.001499184872955084</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0008510809857398272</v>
+        <v>0.0105127040296793</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001461000530980527</v>
+        <v>0.007769523188471794</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001897440408356488</v>
+        <v>0.01596572995185852</v>
       </c>
       <c r="W8" t="n">
-        <v>0.005078647751361132</v>
+        <v>0.009893877431750298</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002296457998454571</v>
+        <v>0.02607617154717445</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003313455265015364</v>
+        <v>0.008562268689274788</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01190954260528088</v>
+        <v>0.001731037627905607</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002178217750042677</v>
+        <v>0.0005276288138702512</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001464045606553555</v>
+        <v>0.001250799046829343</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.007280017249286175</v>
+        <v>0.0009898463031277061</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002876053564250469</v>
+        <v>0.01059647463262081</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.006511250510811806</v>
+        <v>0.01376183517277241</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004072072915732861</v>
+        <v>0.03249898925423622</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0004628608585335314</v>
+        <v>0.00967663899064064</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0001904226373881102</v>
+        <v>0.009488689713180065</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.003480235813185573</v>
+        <v>0.01562652736902237</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8.57451232150197e-05</v>
+        <v>0.01986023411154747</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.002080516889691353</v>
+        <v>0.0004824153147637844</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.007855117321014404</v>
+        <v>0.001620218623429537</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.003583422861993313</v>
+        <v>0.008674783632159233</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.003941907547414303</v>
+        <v>0.02770625613629818</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002420928794890642</v>
+        <v>0.001553184585645795</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.00362112233415246</v>
+        <v>0.002179046859964728</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.007089733146131039</v>
+        <v>0.01816810108721256</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001056208042427897</v>
+        <v>0.005995023995637894</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002852645702660084</v>
+        <v>0.002996536903083324</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001522477949038148</v>
+        <v>0.005025751888751984</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.002467046026140451</v>
+        <v>0.00784745067358017</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.01526761706918478</v>
+        <v>0.04166341200470924</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.03063450939953327</v>
+        <v>0.05917256325483322</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001505774795077741</v>
+        <v>0.01872793398797512</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.008550367318093777</v>
+        <v>0.02554428577423096</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001147089991718531</v>
+        <v>0.0179623831063509</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.01235655695199966</v>
+        <v>0.01267724577337503</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.007408794946968555</v>
+        <v>0.007823845371603966</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0216121282428503</v>
+        <v>0.02202971465885639</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.006885392591357231</v>
+        <v>0.001344446674920619</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.00355174345895648</v>
+        <v>0.0005784677341580391</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.008877137675881386</v>
+        <v>0.03490827977657318</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01679675094783306</v>
+        <v>0.03124229237437248</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.633724403101951e-05</v>
+        <v>0.02301575988531113</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01419471949338913</v>
+        <v>0.01600296422839165</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.02459491789340973</v>
+        <v>0.009698622860014439</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.00381875759921968</v>
+        <v>0.02509519457817078</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.002392822178080678</v>
+        <v>0.0005719331093132496</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.004766530822962523</v>
+        <v>0.005029493011534214</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.006421625148504972</v>
+        <v>0.007414983585476875</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.007597910240292549</v>
+        <v>0.009355748072266579</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01283689867705107</v>
+        <v>0.01169903762638569</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.002421798417344689</v>
+        <v>0.006745079532265663</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.007956276647746563</v>
+        <v>0.001188990427181125</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.00352914072573185</v>
+        <v>0.004997290670871735</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.006576939020305872</v>
+        <v>0.00486226798966527</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001052474486641586</v>
+        <v>0.002153691137209535</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.004239091649651527</v>
+        <v>0.009320711717009544</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.007380093447864056</v>
+        <v>0.02055934630334377</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0142284007743001</v>
+        <v>0.06000667810440063</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.004922912456095219</v>
+        <v>0.006200910080224276</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001749335788190365</v>
+        <v>0.003274801652878523</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.005406148731708527</v>
+        <v>0.01196678262203932</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.01606329157948494</v>
+        <v>0.0007396243163384497</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.007795773912221193</v>
+        <v>0.004695117007941008</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.003544878680258989</v>
+        <v>0.0009781612316146493</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.005354229360818863</v>
+        <v>0.006229307502508163</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.006393481977283955</v>
+        <v>0.01167377363890409</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.007693835999816656</v>
+        <v>0.02203494496643543</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.005914546549320221</v>
+        <v>0.006637405604124069</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.004087897948920727</v>
+        <v>0.005184144712984562</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002788354642689228</v>
+        <v>0.002249997109174728</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.003026415826752782</v>
+        <v>0.000888338778167963</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.006094793789088726</v>
+        <v>0.002496005268767476</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0080685680732131</v>
+        <v>0.002631823997944593</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0005552421789616346</v>
+        <v>0.01451656315475702</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001008338644169271</v>
+        <v>0.0007060651551000774</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.007389403413981199</v>
+        <v>0.01039102487266064</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0001069584395736456</v>
+        <v>0.04038722068071365</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.008284963667392731</v>
+        <v>0.001491959090344608</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.004295686725527048</v>
+        <v>0.009751535952091217</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.007835622876882553</v>
+        <v>0.01131335366517305</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.004297815728932619</v>
+        <v>0.0219159834086895</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.003549328539520502</v>
+        <v>0.003585939994081855</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.003667464945465326</v>
+        <v>0.0009577969904057682</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.003864697180688381</v>
+        <v>0.01141146384179592</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.005293595604598522</v>
+        <v>0.02238771691918373</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.006953770760446787</v>
+        <v>0.006827368400990963</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.003879642114043236</v>
+        <v>0.008500273339450359</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001440430525690317</v>
+        <v>0.0043898094445467</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001100313966162503</v>
+        <v>0.002964506391435862</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.00656094029545784</v>
+        <v>7.175287464633584e-06</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.004560726694762707</v>
+        <v>0.003340351628139615</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02360332757234573</v>
+        <v>0.003001189790666103</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.001575520262122154</v>
+        <v>0.03222021833062172</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.009110104292631149</v>
+        <v>0.01903920993208885</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001349778263829648</v>
+        <v>0.01567481085658073</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01270156446844339</v>
+        <v>0.008970377966761589</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.02122048288583755</v>
+        <v>0.007743465714156628</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001510646776296198</v>
+        <v>0.03505170345306396</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.001902846386656165</v>
+        <v>0.0161932073533535</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.002718122908845544</v>
+        <v>0.003478796221315861</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.004546144977211952</v>
+        <v>0.0001078706991393119</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.005816465709358454</v>
+        <v>6.082869367673993e-05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0006191793363541365</v>
+        <v>0.01133155170828104</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01061334181576967</v>
+        <v>0.01726718619465828</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001071234000846744</v>
+        <v>0.0002504566218703985</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001139640109613538</v>
+        <v>0.006278584711253643</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.006150660570710897</v>
+        <v>0.008151172660291195</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.005972927436232567</v>
+        <v>0.02480237931013107</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001223722589202225</v>
+        <v>0.01176655665040016</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0003348889877088368</v>
+        <v>0.002947306726127863</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001712667755782604</v>
+        <v>0.001487445551902056</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.006052144337445498</v>
+        <v>0.001350949984043837</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.00129022472538054</v>
+        <v>0.01041693426668644</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.007119918242096901</v>
+        <v>0.01205429807305336</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.004175812937319279</v>
+        <v>0.008617931976914406</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.008814328350126743</v>
+        <v>0.02666540071368217</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001252903486602008</v>
+        <v>0.01103590056300163</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.004572975914925337</v>
+        <v>0.002946979831904173</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.005887603387236595</v>
+        <v>0.001855615060776472</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.007063616998493671</v>
+        <v>0.008872237987816334</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.01028730999678373</v>
+        <v>0.01580827310681343</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.001198569778352976</v>
+        <v>0.008881367743015289</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.002660041209310293</v>
+        <v>0.003971883561462164</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001939205918461084</v>
+        <v>0.004552391357719898</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.003507736837491393</v>
+        <v>0.0008215057896450162</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.009058592841029167</v>
+        <v>0.004185771103948355</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.004605358466506004</v>
+        <v>0.00286292121745646</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0002695514122024179</v>
+        <v>0.0100579559803009</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.006834009662270546</v>
+        <v>0.002660867525264621</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.002382287755608559</v>
+        <v>0.01870709285140038</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.004991975612938404</v>
+        <v>0.00675152987241745</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.001261233119294047</v>
+        <v>0.02973394654691219</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.001149650663137436</v>
+        <v>0.00764140672981739</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0159839354455471</v>
+        <v>0.01000422984361649</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.009588412940502167</v>
+        <v>0.007439505308866501</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.002813916187733412</v>
+        <v>0.0005121227586641908</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.00450535211712122</v>
+        <v>0.006816379260271788</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.005130200646817684</v>
+        <v>0.01122845057398081</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.006155728362500668</v>
+        <v>0.02527876198291779</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.00524555891752243</v>
+        <v>0.008361035026609898</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.004866661503911018</v>
+        <v>0.006835056468844414</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0004735596012324095</v>
+        <v>0.004694042261689901</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001499751349911094</v>
+        <v>0.006383315660059452</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.007572895847260952</v>
+        <v>0.0001684942399151623</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.001231385162100196</v>
+        <v>0.003367725526914001</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.001803479506634176</v>
+        <v>0.002343207597732544</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001026223879307508</v>
+        <v>0.01972587406635284</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.006489529740065336</v>
+        <v>0.01639599166810513</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00441609974950552</v>
+        <v>0.002141545992344618</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.001160804065875709</v>
+        <v>0.01521395798772573</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.004079974256455898</v>
+        <v>0.0007335061673074961</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.002544890157878399</v>
+        <v>0.01318524777889252</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.005432458594441414</v>
+        <v>0.01420772448182106</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01205398887395859</v>
+        <v>0.00532878190279007</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.003753493307158351</v>
+        <v>0.000573201454244554</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.01987813971936703</v>
+        <v>0.007672639098018408</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.01337154395878315</v>
+        <v>0.02951615676283836</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001609934726729989</v>
+        <v>0.004776003770530224</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.008513370528817177</v>
+        <v>6.815174128860235e-05</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.001384571194648743</v>
+        <v>0.01571882143616676</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0009362837881781161</v>
+        <v>0.009094302542507648</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.005111416801810265</v>
+        <v>0.009241500869393349</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.003386039519682527</v>
+        <v>0.001309561543166637</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.005573143251240253</v>
+        <v>0.02054430358111858</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.009225045330822468</v>
+        <v>0.01549133006483316</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.00215636333450675</v>
+        <v>0.01949840411543846</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.007380125112831593</v>
+        <v>0.01703557372093201</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01118589006364346</v>
+        <v>0.007352679502218962</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.002180470852181315</v>
+        <v>0.01893804036080837</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.00477986503392458</v>
+        <v>0.002140913158655167</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.003868399187922478</v>
+        <v>0.003687263932079077</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0007145153358578682</v>
+        <v>0.0006096677388995886</v>
       </c>
       <c r="B10" t="n">
-        <v>0.111066035926342</v>
+        <v>0.002755928784608841</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01409697160124779</v>
+        <v>0.0008835176704451442</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03596542030572891</v>
+        <v>8.072142372839153e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07257011532783508</v>
+        <v>0.001271750894375145</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02990218065679073</v>
+        <v>0.002537325490266085</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003545316169038415</v>
+        <v>0.0006822145078331232</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01378902513533831</v>
+        <v>0.0006942381151020527</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004907175898551941</v>
+        <v>0.0006635886384174228</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004308653995394707</v>
+        <v>0.000729160790797323</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0857880562543869</v>
+        <v>0.003863941645249724</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006497784052044153</v>
+        <v>0.0006567761884070933</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01948477700352669</v>
+        <v>0.000697992043569684</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05797821283340454</v>
+        <v>0.002191497711464763</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03425315022468567</v>
+        <v>0.002867685165256262</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003478616243228316</v>
+        <v>0.0001293238019570708</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01364424731582403</v>
+        <v>0.001077845110557973</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003955431282520294</v>
+        <v>0.001650189165957272</v>
       </c>
       <c r="S10" t="n">
-        <v>0.000132773770019412</v>
+        <v>0.0006788118043914437</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01706431619822979</v>
+        <v>0.0005928523605689406</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001636651577427983</v>
+        <v>0.0004904641536995769</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01896565221250057</v>
+        <v>0.0008687831577844918</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01667069643735886</v>
+        <v>0.0005895619397051632</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01328211650252342</v>
+        <v>0.0006675177137367427</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.004220565780997276</v>
+        <v>0.0002276593004353344</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01322993449866772</v>
+        <v>0.0007536500343121588</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001355894608423114</v>
+        <v>0.0002535703824833035</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.004186716862022877</v>
+        <v>0.001518357894383371</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01574066653847694</v>
+        <v>0.0001025428937282413</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.006502728909254074</v>
+        <v>0.0003320261894259602</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.002771473722532392</v>
+        <v>0.000801068963482976</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01107215695083141</v>
+        <v>0.001852818764746189</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003918816335499287</v>
+        <v>0.0008798963390290737</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01939511671662331</v>
+        <v>0.0008792590815573931</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.00231220992282033</v>
+        <v>0.001699549145996571</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0051009776070714</v>
+        <v>0.0001931847655214369</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.01669132150709629</v>
+        <v>0.0007283065933734179</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01960814744234085</v>
+        <v>0.0004571196623146534</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.007771105505526066</v>
+        <v>0.0002787279081530869</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001855963841080666</v>
+        <v>0.0005208002403378487</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01355628110468388</v>
+        <v>0.0007124667754396796</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.01302881632000208</v>
+        <v>0.0002011236356338486</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.009681655094027519</v>
+        <v>0.0002764468663372099</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.003984969109296799</v>
+        <v>0.001059023663401604</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.007492547389119864</v>
+        <v>0.0004293729143682867</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01173795387148857</v>
+        <v>0.0002081815910059959</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.09686923772096634</v>
+        <v>0.004645559471100569</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.00447749812155962</v>
+        <v>0.0003223177627660334</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.005040726158767939</v>
+        <v>0.0001878272014437243</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.02178379893302917</v>
+        <v>0.0003678169741760939</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02504735067486763</v>
+        <v>0.002049474744126201</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.01457495242357254</v>
+        <v>0.0003143468056805432</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01556091476231813</v>
+        <v>0.0001522606034995988</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.01202262938022614</v>
+        <v>0.0008255854481831193</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01124613173305988</v>
+        <v>0.0007557739736512303</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02813562378287315</v>
+        <v>0.0005070193437859416</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.01460913009941578</v>
+        <v>0.0003570195403881371</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.004111302550882101</v>
+        <v>0.0004783558542840183</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.04509912431240082</v>
+        <v>0.0001621689589228481</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01655287854373455</v>
+        <v>0.0005004776758141816</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.007755747064948082</v>
+        <v>0.00030785336275585</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.02190930582582951</v>
+        <v>0.0007256916142068803</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.01314252242445946</v>
+        <v>0.0002112949441652745</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01731503009796143</v>
+        <v>0.0004179112147539854</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04189876466989517</v>
+        <v>0.001411397708579898</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.01136523578315973</v>
+        <v>0.0002299403276992962</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.009987780824303627</v>
+        <v>0.000112402718514204</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02704879269003868</v>
+        <v>0.001762138563208282</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01746845804154873</v>
+        <v>0.001100620254874229</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.01129416283220053</v>
+        <v>0.001236949465237558</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.003044801531359553</v>
+        <v>0.0003078250447288156</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002462596632540226</v>
+        <v>0.0008290882688015699</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.008461708202958107</v>
+        <v>0.0005382100935094059</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05575838312506676</v>
+        <v>0.002791693899780512</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0220642052590847</v>
+        <v>0.0001131540047936141</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.006813678424805403</v>
+        <v>0.001443219836801291</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.009628197178244591</v>
+        <v>8.17263571661897e-05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.01072103437036276</v>
+        <v>0.0009540107566863298</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.00965237058699131</v>
+        <v>0.0002169691142626107</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003510887268930674</v>
+        <v>0.0001001603668555617</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.003651980776339769</v>
+        <v>0.0001914923923322931</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.002737950766459107</v>
+        <v>0.0006825700402259827</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01866769045591354</v>
+        <v>0.000861270003952086</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002874454716220498</v>
+        <v>0.0003363639989402145</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.009366840124130249</v>
+        <v>0.0001066958357114345</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006580800749361515</v>
+        <v>0.0002130804641637951</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.006592723075300455</v>
+        <v>0.0007623487617820501</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.008302910253405571</v>
+        <v>0.0004722410521935672</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.003638043068349361</v>
+        <v>1.868017352535389e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0005791594740003347</v>
+        <v>5.010155655327253e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.03318771719932556</v>
+        <v>0.0002798503846861422</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.03248079121112823</v>
+        <v>0.00252755987457931</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.001779870712198317</v>
+        <v>0.0002343153464607894</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.01080205291509628</v>
+        <v>1.443106157239527e-05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01586698926985264</v>
+        <v>0.0009895999683067203</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.003511491930112243</v>
+        <v>0.000300309737212956</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.006715384777635336</v>
+        <v>0.0006271660095080733</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01010056585073471</v>
+        <v>0.0001221912098117173</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004451541695743799</v>
+        <v>0.0001988914154935628</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.001993059879168868</v>
+        <v>0.0004260454443283379</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.01300361473113298</v>
+        <v>0.0007473505102097988</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.006210203282535076</v>
+        <v>0.0002198647998739034</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01482141204178333</v>
+        <v>4.121739766560495e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.00454974640160799</v>
+        <v>0.0002353874006075785</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.008224179036915302</v>
+        <v>0.0008225546916946769</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.006936786696314812</v>
+        <v>0.0001354607084067538</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.005893640220165253</v>
+        <v>1.698169216979295e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0008207736536860466</v>
+        <v>0.0001068150813807733</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.008840639144182205</v>
+        <v>0.0001629642501939088</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.02489189803600311</v>
+        <v>0.001701222499832511</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.00689358776435256</v>
+        <v>0.0003755003563128412</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.05796600878238678</v>
+        <v>2.881631371565163e-05</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01828582212328911</v>
+        <v>0.0004754567053169012</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0006616862374357879</v>
+        <v>0.0003077150322496891</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.03062485344707966</v>
+        <v>0.0007228084723465145</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001574687659740448</v>
+        <v>0.001115807564929128</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.01654247753322124</v>
+        <v>1.851464185165241e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.01180409453809261</v>
+        <v>9.023118764162064e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0153455538675189</v>
+        <v>0.0002824025868903846</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.007627410348504782</v>
+        <v>0.0001468963746447116</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0005441084504127502</v>
+        <v>0.001152183511294425</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001300462987273932</v>
+        <v>0.0007691195351071656</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0126147260889411</v>
+        <v>0.0001694531820248812</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.003560156328603625</v>
+        <v>0.0002410708257229999</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.00377400778234005</v>
+        <v>0.001026076730340719</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.004239615984261036</v>
+        <v>0.0001588274608366191</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.005682844668626785</v>
+        <v>0.0003561456978786737</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.007664564996957779</v>
+        <v>0.0001585480058565736</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0007029332919046283</v>
+        <v>6.967876106500626e-05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.00796432513743639</v>
+        <v>0.0002328132250113413</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.007070688996464014</v>
+        <v>0.0004585969727486372</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.009112781845033169</v>
+        <v>0.0006880288710817695</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.005036673508584499</v>
+        <v>0.0003293817571830004</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.006879143882542849</v>
+        <v>0.0001892556319944561</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.004178850911557674</v>
+        <v>0.00066172587685287</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.005860789678990841</v>
+        <v>0.0005040703690610826</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01038152817636728</v>
+        <v>2.660501195350662e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.001587348757311702</v>
+        <v>0.0004037216422148049</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.005353610962629318</v>
+        <v>0.0003795810916926712</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01074772235006094</v>
+        <v>0.0002452746848575771</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0006758629460819066</v>
+        <v>0.000733701977878809</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.009447522461414337</v>
+        <v>0.0003458752471487969</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.001448404043912888</v>
+        <v>0.0001750764204189181</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0008739473996683955</v>
+        <v>0.0001102892492781393</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01533794403076172</v>
+        <v>0.0006686956039629877</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.006612460594624281</v>
+        <v>0.0004214842338114977</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.016566077247262</v>
+        <v>3.615823516156524e-06</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01707004196941853</v>
+        <v>0.0005016057402826846</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.004943756386637688</v>
+        <v>0.0008990472415462136</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.01750470511615276</v>
+        <v>0.0002414112677797675</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004857252817600965</v>
+        <v>0.0003515392600093037</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01586753502488136</v>
+        <v>1.574646375956945e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.005331079475581646</v>
+        <v>0.0001212201459566131</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.001520745339803398</v>
+        <v>0.0005880726967006922</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.009627314284443855</v>
+        <v>0.001074235769920051</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.003051149658858776</v>
+        <v>0.000266647373791784</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01004036143422127</v>
+        <v>3.276276402175426e-06</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.005420113913714886</v>
+        <v>2.845905873982701e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.009295642375946045</v>
+        <v>0.0006114678690209985</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.01036499254405499</v>
+        <v>0.0004666857130359858</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.004140066914260387</v>
+        <v>5.289092223392799e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.002866815077140927</v>
+        <v>0.0001604806020623073</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.004556944128125906</v>
+        <v>0.0002051380288321525</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01542029157280922</v>
+        <v>0.001075382344424725</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.008228030055761337</v>
+        <v>0.0003656944027170539</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.008222132921218872</v>
+        <v>0.0007380518945865333</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.005356168374419212</v>
+        <v>0.0002019220555666834</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.005900595337152481</v>
+        <v>0.0005144840106368065</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.008335321210324764</v>
+        <v>0.0005260095931589603</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.004210355691611767</v>
+        <v>0.001086143078282475</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.002470988780260086</v>
+        <v>0.0004778680158779025</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.02140801958739758</v>
+        <v>0.0004136257339268923</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.006678221747279167</v>
+        <v>0.0002812727761920542</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.004951855633407831</v>
+        <v>0.0008399622165597975</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.02018103376030922</v>
+        <v>0.0008084325818344951</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.003346230369061232</v>
+        <v>0.0004755009431391954</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.007410686463117599</v>
+        <v>0.0002604206092655659</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.004729448352009058</v>
+        <v>0.0002220407186541706</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0009545005159452558</v>
+        <v>0.001582347555086017</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.008876550011336803</v>
+        <v>0.001162607921287417</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.01257031131535769</v>
+        <v>0.001092921826057136</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.01676477864384651</v>
+        <v>1.930687722051516e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01473066583275795</v>
+        <v>0.0002872385666705668</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.001586069585755467</v>
+        <v>9.665538527769968e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0004209660110063851</v>
+        <v>0.0003909407532773912</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.01726579293608665</v>
+        <v>0.001405030838213861</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.02635040134191513</v>
+        <v>6.05487912253011e-06</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0114348353818059</v>
+        <v>0.000910744653083384</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.004003601148724556</v>
+        <v>0.000478771107736975</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.02783453278243542</v>
+        <v>0.09694576263427734</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1192137748003006</v>
+        <v>0.3781537413597107</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005695431493222713</v>
+        <v>0.02087107300758362</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06601305305957794</v>
+        <v>0.4685181975364685</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0730426013469696</v>
+        <v>0.06973724812269211</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04919812083244324</v>
+        <v>0.2094526886940002</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02477268502116203</v>
+        <v>0.2469100207090378</v>
       </c>
       <c r="H11" t="n">
-        <v>0.008034047670662403</v>
+        <v>0.225935235619545</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02261913754045963</v>
+        <v>0.01398707274347544</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01797423511743546</v>
+        <v>0.03400040417909622</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09613332152366638</v>
+        <v>0.2890211045742035</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00759602477774024</v>
+        <v>0.003544420003890991</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04879481345415115</v>
+        <v>0.7186123132705688</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0653868094086647</v>
+        <v>0.2398591637611389</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04021728783845901</v>
+        <v>0.1945103108882904</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01022833865135908</v>
+        <v>0.2629651129245758</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004362352192401886</v>
+        <v>0.162503257393837</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02880760468542576</v>
+        <v>0.02456537261605263</v>
       </c>
       <c r="S11" t="n">
-        <v>0.004444651305675507</v>
+        <v>0.01848549023270607</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003003096440806985</v>
+        <v>0.01184158679097891</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01629361137747765</v>
+        <v>0.02370440028607845</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03965817019343376</v>
+        <v>0.09577076137065887</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05247281119227409</v>
+        <v>0.01129414513707161</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02353209257125854</v>
+        <v>0.08640790730714798</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.005777088925242424</v>
+        <v>0.01392762735486031</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.017205610871315</v>
+        <v>0.0120201725512743</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0001076840562745929</v>
+        <v>0.06771988421678543</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0003877608105540276</v>
+        <v>0.05689570307731628</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.008907945826649666</v>
+        <v>0.04879378899931908</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02266132272779942</v>
+        <v>0.08147645741701126</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.02416863664984703</v>
+        <v>0.065426304936409</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01110129244625568</v>
+        <v>0.01116012968122959</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02591255679726601</v>
+        <v>0.2158171236515045</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.002727552317082882</v>
+        <v>0.06812466681003571</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01247036643326283</v>
+        <v>0.05581563338637352</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.03429318964481354</v>
+        <v>0.05357859283685684</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.01354164350777864</v>
+        <v>0.01842781715095043</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02052941732108593</v>
+        <v>0.1621255874633789</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.005102844908833504</v>
+        <v>0.1132252216339111</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0148375891149044</v>
+        <v>0.008305281400680542</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01088802050799131</v>
+        <v>0.09614691138267517</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0139771718531847</v>
+        <v>0.06807892769575119</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.003734968602657318</v>
+        <v>0.09901814162731171</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.00540638156235218</v>
+        <v>0.04296405613422394</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0009244869579561055</v>
+        <v>0.04003486782312393</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.01899994909763336</v>
+        <v>0.07154326140880585</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.06570525467395782</v>
+        <v>0.09868558496236801</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.008617164567112923</v>
+        <v>0.1505635380744934</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.03556192293763161</v>
+        <v>0.1601996570825577</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.06835371255874634</v>
+        <v>0.3832219541072845</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.006976628676056862</v>
+        <v>0.190814882516861</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.02716078236699104</v>
+        <v>0.01858919858932495</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.01327284052968025</v>
+        <v>0.006232874467968941</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.01114996150135994</v>
+        <v>0.0811179131269455</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.3637580499053e-05</v>
+        <v>0.1699957549571991</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02653919532895088</v>
+        <v>0.024094108492136</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01445997599512339</v>
+        <v>0.0772925466299057</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.03735595196485519</v>
+        <v>0.09152022004127502</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.04165394231677055</v>
+        <v>0.04816234111785889</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0213238000869751</v>
+        <v>0.04469871520996094</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.01696013100445271</v>
+        <v>0.1087807565927505</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.007681128568947315</v>
+        <v>0.06146054714918137</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02619536221027374</v>
+        <v>0.1099975779652596</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.003147646319121122</v>
+        <v>0.001465881243348122</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.005990066099911928</v>
+        <v>0.00120160449296236</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0003475970006547868</v>
+        <v>0.06748825311660767</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.02453865110874176</v>
+        <v>0.06969211995601654</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01067808549851179</v>
+        <v>0.1045510917901993</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01981600001454353</v>
+        <v>0.06065597012639046</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.001942015951499343</v>
+        <v>0.05139647796750069</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.01603126339614391</v>
+        <v>0.009368250146508217</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.01318797096610069</v>
+        <v>0.004269523546099663</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.02759553492069244</v>
+        <v>0.0389263927936554</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.05354272574186325</v>
+        <v>0.06565073132514954</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.004593872465193272</v>
+        <v>0.07117407023906708</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.04130474850535393</v>
+        <v>0.2140187323093414</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.03429612517356873</v>
+        <v>0.0816451832652092</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02491116710007191</v>
+        <v>0.07313361018896103</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.01134830806404352</v>
+        <v>0.01882410794496536</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.007029022090137005</v>
+        <v>0.01756818778812885</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.01060667634010315</v>
+        <v>0.02784967608749866</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.002724481979385018</v>
+        <v>0.07319952547550201</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0136547926813364</v>
+        <v>0.1237567737698555</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.004392624832689762</v>
+        <v>0.02827171422541142</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02098209783434868</v>
+        <v>0.1630133986473083</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.007872577756643295</v>
+        <v>0.00674128346145153</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01624118350446224</v>
+        <v>0.04285891354084015</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.002145629376173019</v>
+        <v>0.003367958823218942</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.002569205360487103</v>
+        <v>0.07232135534286499</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.005398270674049854</v>
+        <v>0.03356252238154411</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.001270897570066154</v>
+        <v>0.1024875789880753</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.008148624561727047</v>
+        <v>0.07250568270683289</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.006454216782003641</v>
+        <v>0.2946597635746002</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.07333770394325256</v>
+        <v>0.3825941383838654</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.04229051992297173</v>
+        <v>0.1394464075565338</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.003046004101634026</v>
+        <v>0.1203932762145996</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.02143875136971474</v>
+        <v>0.09306024014949799</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01442727912217379</v>
+        <v>0.02775377780199051</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.008388214744627476</v>
+        <v>0.009630890563130379</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002104865154251456</v>
+        <v>0.06556225568056107</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.01261844113469124</v>
+        <v>0.1215727776288986</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.005995731800794601</v>
+        <v>0.007239861413836479</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.01703105866909027</v>
+        <v>0.1721388101577759</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01823738217353821</v>
+        <v>0.03834861889481544</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01943355239927769</v>
+        <v>0.06603001803159714</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.003135349368676543</v>
+        <v>0.0119945015758276</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0040737628005445</v>
+        <v>0.05857585370540619</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001402541762217879</v>
+        <v>0.01401804760098457</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.01081785466521978</v>
+        <v>0.01153494045138359</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.06058783456683159</v>
+        <v>0.02770797163248062</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01287447474896908</v>
+        <v>0.06218431890010834</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.05616502091288567</v>
+        <v>0.1153125539422035</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01289777178317308</v>
+        <v>0.03806288540363312</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.06413862109184265</v>
+        <v>0.2965318560600281</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.004060284234583378</v>
+        <v>0.04108083248138428</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.005235723685473204</v>
+        <v>0.228667750954628</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01688932254910469</v>
+        <v>0.02750283479690552</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.02323019690811634</v>
+        <v>0.06471705436706543</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.009750546887516975</v>
+        <v>0.05959917604923248</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.01690365374088287</v>
+        <v>0.003723246976733208</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.04451315477490425</v>
+        <v>0.009129337966442108</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01413298211991787</v>
+        <v>0.02911069616675377</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.02633297629654408</v>
+        <v>0.01869545318186283</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.02247427217662334</v>
+        <v>0.002459479495882988</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.007805724162608385</v>
+        <v>0.09779861569404602</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0224184226244688</v>
+        <v>0.182600125670433</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.01285659708082676</v>
+        <v>0.007570548914372921</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.009140403009951115</v>
+        <v>0.03157958388328552</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01235316134989262</v>
+        <v>0.1918137669563293</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.01588786765933037</v>
+        <v>0.08596596121788025</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01646394841372967</v>
+        <v>0.1070251762866974</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.006196381989866495</v>
+        <v>0.2324994951486588</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.006336959078907967</v>
+        <v>0.002126317471265793</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.01774077862501144</v>
+        <v>0.1744963526725769</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.005492310505360365</v>
+        <v>0.1504378467798233</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.002094228053465486</v>
+        <v>0.1825650632381439</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.008655315265059471</v>
+        <v>0.06991629302501678</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01214464660733938</v>
+        <v>0.1598739624023438</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.007553096394985914</v>
+        <v>0.2053671330213547</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001086450647562742</v>
+        <v>0.01678285747766495</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.03851592168211937</v>
+        <v>0.04377623647451401</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.007767174858599901</v>
+        <v>0.0044908681884408</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.01296812947839499</v>
+        <v>0.02939250692725182</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.005540556274354458</v>
+        <v>0.0449177548289299</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001947275828570127</v>
+        <v>0.01995557546615601</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.001028515631332994</v>
+        <v>0.19585320353508</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.014313580468297</v>
+        <v>0.09886960685253143</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.01786388084292412</v>
+        <v>0.2098258137702942</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01887581497430801</v>
+        <v>0.1743927299976349</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.07178831100463867</v>
+        <v>0.09490274637937546</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.002419684082269669</v>
+        <v>0.04874753579497337</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.01675079576671124</v>
+        <v>0.09762369096279144</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.009282918646931648</v>
+        <v>0.08465923368930817</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.004844731651246548</v>
+        <v>0.06051413714885712</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0128523102030158</v>
+        <v>0.1373450309038162</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.004998151678591967</v>
+        <v>0.02665295638144016</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.02529247477650642</v>
+        <v>0.2073003947734833</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.007069187238812447</v>
+        <v>0.02679256163537502</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.01767046935856342</v>
+        <v>0.05215689167380333</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.002081917598843575</v>
+        <v>0.01153520494699478</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0004105121188331395</v>
+        <v>0.08325662463903427</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001863888232037425</v>
+        <v>0.007033179979771376</v>
       </c>
       <c r="FG11" t="n">
-        <v>4.332652315497398e-05</v>
+        <v>0.06733699142932892</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.02103676460683346</v>
+        <v>0.05444421991705894</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.02154337614774704</v>
+        <v>0.0008669737726449966</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01037480309605598</v>
+        <v>0.02200441993772984</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01703251898288727</v>
+        <v>0.07408779114484787</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01748435758054256</v>
+        <v>0.01700980961322784</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.02079662494361401</v>
+        <v>0.03761385008692741</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.01051568612456322</v>
+        <v>0.09698228538036346</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0261013749986887</v>
+        <v>0.02910943515598774</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.009565208107233047</v>
+        <v>0.03923727944493294</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.04351428151130676</v>
+        <v>0.2322143316268921</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.05531556159257889</v>
+        <v>0.1169545575976372</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.03193973749876022</v>
+        <v>0.1511157006025314</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01353743858635426</v>
+        <v>0.424273282289505</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01453487575054169</v>
+        <v>0.01636482030153275</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.01322725042700768</v>
+        <v>0.06904460489749908</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.002364386338740587</v>
+        <v>0.1886321753263474</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.005110815167427063</v>
+        <v>0.008050992153584957</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01192257925868034</v>
+        <v>0.04470899701118469</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.01198102813214064</v>
+        <v>0.002032903954386711</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.009289338253438473</v>
+        <v>0.05697345361113548</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.01854562759399414</v>
+        <v>0.2398061603307724</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.06636940687894821</v>
+        <v>0.1087300702929497</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.005525731015950441</v>
+        <v>0.05244490504264832</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.04007720202207565</v>
+        <v>0.08233499526977539</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.006818369496613741</v>
+        <v>0.03649822622537613</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.005917210131883621</v>
+        <v>0.03455943241715431</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.09666554629802704</v>
+        <v>0.2077109217643738</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5666561722755432</v>
+        <v>0.4685592353343964</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01403002440929413</v>
+        <v>0.1327424943447113</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7192530632019043</v>
+        <v>0.2049585431814194</v>
       </c>
       <c r="E12" t="n">
-        <v>0.144292801618576</v>
+        <v>0.05093366652727127</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2614668011665344</v>
+        <v>0.5565517544746399</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1882411986589432</v>
+        <v>0.2022909075021744</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08672395348548889</v>
+        <v>0.3742242753505707</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3275998830795288</v>
+        <v>0.02822565659880638</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1842546761035919</v>
+        <v>0.2773000001907349</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3737974166870117</v>
+        <v>0.4445018768310547</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01062591746449471</v>
+        <v>0.2244328260421753</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5567432641983032</v>
+        <v>0.4182467460632324</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2452139258384705</v>
+        <v>0.2273874580860138</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4004139006137848</v>
+        <v>0.4840270280838013</v>
       </c>
       <c r="P12" t="n">
-        <v>0.126029446721077</v>
+        <v>0.1904213130474091</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01701698265969753</v>
+        <v>0.4052748084068298</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3092542886734009</v>
+        <v>0.02729683369398117</v>
       </c>
       <c r="S12" t="n">
-        <v>0.05940369144082069</v>
+        <v>0.01835223659873009</v>
       </c>
       <c r="T12" t="n">
-        <v>0.09672194719314575</v>
+        <v>0.06695043295621872</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1163911074399948</v>
+        <v>0.2342040538787842</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2043928802013397</v>
+        <v>0.07155066728591919</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1888443827629089</v>
+        <v>0.03054190054535866</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03000873327255249</v>
+        <v>0.05348518490791321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.104473665356636</v>
+        <v>0.02033882774412632</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1950971484184265</v>
+        <v>0.06856885552406311</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1680533140897751</v>
+        <v>0.05473573878407478</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.07264885306358337</v>
+        <v>0.02391039207577705</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.08875422924757004</v>
+        <v>0.228383794426918</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07604563236236572</v>
+        <v>0.03152782469987869</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0012241555377841</v>
+        <v>0.1302588135004044</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05008397623896599</v>
+        <v>0.1242165267467499</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.06785106658935547</v>
+        <v>0.08689127117395401</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1158752292394638</v>
+        <v>0.1152576208114624</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03468780964612961</v>
+        <v>0.06534847617149353</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1595355868339539</v>
+        <v>0.0685662254691124</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0615256242454052</v>
+        <v>0.05474036186933517</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2257899045944214</v>
+        <v>0.09653415530920029</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.01023678481578827</v>
+        <v>0.2457549870014191</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.001827765256166458</v>
+        <v>0.06503474712371826</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03941873461008072</v>
+        <v>0.003796052187681198</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.03279562294483185</v>
+        <v>0.03474214300513268</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0690215677022934</v>
+        <v>0.05224398151040077</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.03677081316709518</v>
+        <v>0.03241545334458351</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.1118898838758469</v>
+        <v>0.1213913410902023</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.07533340156078339</v>
+        <v>0.04487814381718636</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5458341240882874</v>
+        <v>0.2414469122886658</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.07092553377151489</v>
+        <v>0.2688604593276978</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.29111248254776</v>
+        <v>0.062415461987257</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1271030306816101</v>
+        <v>0.5198810696601868</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.1239854916930199</v>
+        <v>0.3208777606487274</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.151570737361908</v>
+        <v>0.01364197675138712</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.07507315278053284</v>
+        <v>0.002016378566622734</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.1837088614702225</v>
+        <v>0.04920954629778862</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.1242782026529312</v>
+        <v>0.04518131911754608</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.08192837238311768</v>
+        <v>0.2322696447372437</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.2010891437530518</v>
+        <v>0.01443937048316002</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.1565120220184326</v>
+        <v>0.07488393783569336</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.2148087471723557</v>
+        <v>0.3035946488380432</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.1793549656867981</v>
+        <v>0.0939168855547905</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.08288207650184631</v>
+        <v>0.04828630387783051</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.02873155847191811</v>
+        <v>0.1427050679922104</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.1361219584941864</v>
+        <v>0.05208371207118034</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.00694417767226696</v>
+        <v>0.0383337140083313</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1646681129932404</v>
+        <v>0.1101284474134445</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.1423732340335846</v>
+        <v>0.02182408235967159</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05394769459962845</v>
+        <v>0.02222898043692112</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.04218883067369461</v>
+        <v>0.03331132605671883</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0567091628909111</v>
+        <v>0.03103272803127766</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0005670003592967987</v>
+        <v>0.1374374032020569</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01505215093493462</v>
+        <v>0.0019383504986763</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.09331595897674561</v>
+        <v>0.005504122003912926</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.08014549314975739</v>
+        <v>0.05962029844522476</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3627381324768066</v>
+        <v>0.01934899389743805</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.1289366483688354</v>
+        <v>0.2413032650947571</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.3019004464149475</v>
+        <v>0.1272570639848709</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.1518889963626862</v>
+        <v>0.09410501271486282</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01555987633764744</v>
+        <v>0.1849790215492249</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.08585503697395325</v>
+        <v>0.08668909966945648</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.03967424482107162</v>
+        <v>0.04996752738952637</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.2144716382026672</v>
+        <v>0.007473071105778217</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.03053701296448708</v>
+        <v>0.02147795632481575</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.04236303642392159</v>
+        <v>0.1136332899332047</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.1361896842718124</v>
+        <v>0.02668661624193192</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1285027265548706</v>
+        <v>0.04984420910477638</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01386986300349236</v>
+        <v>0.001127646304666996</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.08213552832603455</v>
+        <v>0.1468074768781662</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.01814742013812065</v>
+        <v>0.03437168896198273</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0162659827619791</v>
+        <v>0.08413250744342804</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.07944407314062119</v>
+        <v>0.07223452627658844</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.09236112982034683</v>
+        <v>0.04984316974878311</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.04501552879810333</v>
+        <v>0.07940090447664261</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.09773615747690201</v>
+        <v>0.2341291308403015</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.08900231868028641</v>
+        <v>0.06100264191627502</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.08313791453838348</v>
+        <v>0.1274345815181732</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.2413889169692993</v>
+        <v>0.02354906499385834</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.1489372849464417</v>
+        <v>0.08005985617637634</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.006284761242568493</v>
+        <v>0.02572483941912651</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.1077622100710869</v>
+        <v>0.003426591400057077</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.02388835325837135</v>
+        <v>0.02061973884701729</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.04962355270981789</v>
+        <v>0.08363491296768188</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.1267956048250198</v>
+        <v>0.01121788658201694</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1491245925426483</v>
+        <v>0.05677678063511848</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.986405838280916e-05</v>
+        <v>0.01763509586453438</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1308717578649521</v>
+        <v>0.1410151869058609</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.04199987649917603</v>
+        <v>0.02764065377414227</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.06374893337488174</v>
+        <v>0.09118804335594177</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.02441375143826008</v>
+        <v>0.0690268874168396</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.02590355090796947</v>
+        <v>0.06911811977624893</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.05961361527442932</v>
+        <v>0.003397606313228607</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.02773204073309898</v>
+        <v>0.03795377165079117</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.4036785662174225</v>
+        <v>0.1009927839040756</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.008607608266174793</v>
+        <v>0.1348723173141479</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.3303596973419189</v>
+        <v>0.3791118860244751</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.003645777702331543</v>
+        <v>0.06443352997303009</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.06179098784923553</v>
+        <v>0.08572935312986374</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.1554031223058701</v>
+        <v>0.1456871926784515</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0276599358767271</v>
+        <v>0.01559894531965256</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.04592126607894897</v>
+        <v>0.1238716691732407</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.008618693798780441</v>
+        <v>0.0556824803352356</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.08957748115062714</v>
+        <v>0.05542399734258652</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.02755921334028244</v>
+        <v>0.04656579345464706</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.07060455530881882</v>
+        <v>0.01840386539697647</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1451726257801056</v>
+        <v>0.08170637488365173</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.008824562653899193</v>
+        <v>0.06555752456188202</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.2186432927846909</v>
+        <v>0.01809968799352646</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.03559484705328941</v>
+        <v>0.04401932284235954</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.06342457234859467</v>
+        <v>0.05830838158726692</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.1418058276176453</v>
+        <v>0.1465655267238617</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.1379752457141876</v>
+        <v>0.01503144018352032</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.02953107096254826</v>
+        <v>0.09246378391981125</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.03860807791352272</v>
+        <v>0.1606982350349426</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.03334014862775803</v>
+        <v>0.02386355400085449</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.1001552566885948</v>
+        <v>0.01676009967923164</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.1474481672048569</v>
+        <v>0.07010482251644135</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.05140886083245277</v>
+        <v>0.02461399883031845</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.01435520872473717</v>
+        <v>0.02328204363584518</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.1497894823551178</v>
+        <v>0.06871561706066132</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.07861195504665375</v>
+        <v>0.08821724355220795</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02102830819785595</v>
+        <v>0.0638422891497612</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.151550680398941</v>
+        <v>0.147906094789505</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.01444538589566946</v>
+        <v>0.01437636930495501</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.07165887206792831</v>
+        <v>0.04915009066462517</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.002507697325199842</v>
+        <v>0.08732850104570389</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.04174325987696648</v>
+        <v>0.01408862322568893</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.06323274224996567</v>
+        <v>0.06303939968347549</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.1002791821956635</v>
+        <v>0.0897422656416893</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.05628332868218422</v>
+        <v>0.07083413004875183</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02968720719218254</v>
+        <v>0.03504706919193268</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.207510843873024</v>
+        <v>0.03885485231876373</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.07435087859630585</v>
+        <v>0.04783353209495544</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.06762930750846863</v>
+        <v>0.09052754938602448</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.007294413633644581</v>
+        <v>0.07097338885068893</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.01209015399217606</v>
+        <v>0.0171164944767952</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0357331708073616</v>
+        <v>0.135454922914505</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.1143086850643158</v>
+        <v>0.02781888470053673</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.1698194891214371</v>
+        <v>0.05571244657039642</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0004669715999625623</v>
+        <v>0.008485168218612671</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.09682168066501617</v>
+        <v>0.1198231503367424</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.05657102912664413</v>
+        <v>0.03519931808114052</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.001390863209962845</v>
+        <v>0.09529685229063034</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.07574377954006195</v>
+        <v>0.05353650450706482</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.03614454716444016</v>
+        <v>0.07313183695077896</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01774108037352562</v>
+        <v>0.1033668220043182</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.05196620896458626</v>
+        <v>0.1848451495170593</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.03544648364186287</v>
+        <v>0.05321387574076653</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.08401897549629211</v>
+        <v>0.05925789475440979</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0005629071965813637</v>
+        <v>0.08688606321811676</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06037409976124763</v>
+        <v>0.01449280232191086</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.04489265382289886</v>
+        <v>0.1943432241678238</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.06671370565891266</v>
+        <v>0.05975862964987755</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.02768057025969028</v>
+        <v>0.09179513156414032</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.08322539925575256</v>
+        <v>0.2072957009077072</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.03976264595985413</v>
+        <v>0.273388683795929</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.2193363010883331</v>
+        <v>0.07517816126346588</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.1078132092952728</v>
+        <v>0.1347319036722183</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.1167354881763458</v>
+        <v>0.05539021641016006</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.1208330392837524</v>
+        <v>0.2248668968677521</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.05974160134792328</v>
+        <v>0.07613272219896317</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.05369953811168671</v>
+        <v>0.1757346987724304</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.1207876652479172</v>
+        <v>0.02238457277417183</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.05413390323519707</v>
+        <v>0.1119033172726631</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.1374504566192627</v>
+        <v>0.1833981871604919</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.007601168006658554</v>
+        <v>0.027286347001791</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.1590022593736649</v>
+        <v>0.3254324793815613</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.06773366034030914</v>
+        <v>0.2182631492614746</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.5297370553016663</v>
+        <v>0.01074473932385445</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.05236758664250374</v>
+        <v>0.09681081026792526</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.003390021622180939</v>
+        <v>0.1019724830985069</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.002080370672047138</v>
+        <v>0.01087231002748013</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01258325111120939</v>
+        <v>0.398803174495697</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0009234099416062236</v>
+        <v>0.001414604485034943</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01305533107370138</v>
+        <v>0.2983210682868958</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00641298945993185</v>
+        <v>0.2255310565233231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004313028883188963</v>
+        <v>0.09977031499147415</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004045373760163784</v>
+        <v>0.03866688907146454</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007575667696073651</v>
+        <v>0.09143365919589996</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002185535617172718</v>
+        <v>0.004198925569653511</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001834781956858933</v>
+        <v>0.005967422854155302</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01076766289770603</v>
+        <v>0.4388770461082458</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000386673491448164</v>
+        <v>0.02116779983043671</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008597916923463345</v>
+        <v>0.3777050673961639</v>
       </c>
       <c r="N13" t="n">
-        <v>0.004467890597879887</v>
+        <v>0.2578633725643158</v>
       </c>
       <c r="O13" t="n">
-        <v>0.003645761404186487</v>
+        <v>0.1532838940620422</v>
       </c>
       <c r="P13" t="n">
-        <v>0.004312280565500259</v>
+        <v>0.03214137256145477</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001759860664606094</v>
+        <v>0.04005986452102661</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001848865300416946</v>
+        <v>0.03318784385919571</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0005323252407833934</v>
+        <v>0.01481181941926479</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002308001508936286</v>
+        <v>0.05441087484359741</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003138643456622958</v>
+        <v>0.0504072941839695</v>
       </c>
       <c r="V13" t="n">
-        <v>0.004272224847227335</v>
+        <v>0.09625859558582306</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003235800191760063</v>
+        <v>0.002494831569492817</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003126200754195452</v>
+        <v>0.0497286356985569</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0009012646041810513</v>
+        <v>0.01940637081861496</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002211190760135651</v>
+        <v>0.05136863887310028</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.000231933212489821</v>
+        <v>0.06579495221376419</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003117661690339446</v>
+        <v>0.01557338051497936</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.002411828842014074</v>
+        <v>0.06670912355184555</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.002377065131440759</v>
+        <v>0.07108660042285919</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.004263085313141346</v>
+        <v>0.1024643033742905</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001677476102486253</v>
+        <v>0.2083627581596375</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00179852161090821</v>
+        <v>0.07473433762788773</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0002645051572471857</v>
+        <v>0.03829037770628929</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.002478953450918198</v>
+        <v>0.1073138490319252</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001816352712921798</v>
+        <v>0.02854320034384727</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.002219523536041379</v>
+        <v>0.02548591606318951</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.002555751241743565</v>
+        <v>0.08602502942085266</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.000344418833265081</v>
+        <v>0.03220800682902336</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.000725508900359273</v>
+        <v>0.058405552059412</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.002207467798143625</v>
+        <v>0.151931419968605</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.001578445313498378</v>
+        <v>0.01232989504933357</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001556748757138848</v>
+        <v>0.08288160711526871</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001059644855558872</v>
+        <v>0.07694176584482193</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0003584911464713514</v>
+        <v>0.01216509658843279</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.002869294956326485</v>
+        <v>0.06285510957241058</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.005986679811030626</v>
+        <v>0.2642664909362793</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0001015792950056493</v>
+        <v>0.04567915946245193</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.005457682069391012</v>
+        <v>0.09866005182266235</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.004991800058633089</v>
+        <v>0.1206998452544212</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.002267710398882627</v>
+        <v>0.1059979870915413</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.002108003245666623</v>
+        <v>0.0435793399810791</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.003265776438638568</v>
+        <v>0.0002645049244165421</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.001724861795082688</v>
+        <v>0.02277194336056709</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.001521994359791279</v>
+        <v>0.03889726847410202</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.004600930493324995</v>
+        <v>0.05258478224277496</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.002060942584648728</v>
+        <v>0.07991892099380493</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.00572574557736516</v>
+        <v>0.04814279451966286</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.00204526586458087</v>
+        <v>0.1857617497444153</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.002923771739006042</v>
+        <v>0.02387775853276253</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.001868747407570481</v>
+        <v>0.01485374197363853</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.001063313102349639</v>
+        <v>0.01102283596992493</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.00118923035915941</v>
+        <v>0.003459786996245384</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.003646989818662405</v>
+        <v>0.0286381971091032</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.001081992872059345</v>
+        <v>0.0661570131778717</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0007089398568496108</v>
+        <v>0.05491612106561661</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.002315685153007507</v>
+        <v>0.07162455469369888</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.002344429958611727</v>
+        <v>0.006924829445779324</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.003129385877400637</v>
+        <v>0.01208217535167933</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.002983642974868417</v>
+        <v>0.01401730813086033</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0006989650428295135</v>
+        <v>0.1013971790671349</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0009793131612241268</v>
+        <v>0.07503698766231537</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.003896054113283753</v>
+        <v>0.03619583696126938</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.004260050598531961</v>
+        <v>0.2881861925125122</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.000452881446108222</v>
+        <v>0.02166533097624779</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.003141648136079311</v>
+        <v>0.2148931920528412</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.373092325404286e-06</v>
+        <v>0.008436188101768494</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.005007043480873108</v>
+        <v>0.01257043518126011</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.002030300442129374</v>
+        <v>0.03870661929249763</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0001168751914519817</v>
+        <v>0.01615889370441437</v>
       </c>
       <c r="CC13" t="n">
-        <v>7.064713281579316e-05</v>
+        <v>0.05979719385504723</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0007749549695290625</v>
+        <v>0.009989363141357899</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0006706573185510933</v>
+        <v>0.1551538407802582</v>
       </c>
       <c r="CF13" t="n">
-        <v>4.909159179078415e-05</v>
+        <v>0.000823974609375</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.00337670324370265</v>
+        <v>0.07967830449342728</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001156184589490294</v>
+        <v>0.007150075398385525</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.002185510937124491</v>
+        <v>0.00237591564655304</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0004599181411322206</v>
+        <v>0.0232867393642664</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0002286338130943477</v>
+        <v>0.01305864658206701</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0008173417882062495</v>
+        <v>0.02794397249817848</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.001753337681293488</v>
+        <v>0.01502705737948418</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001379540539346635</v>
+        <v>0.2179118096828461</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.00181967148091644</v>
+        <v>0.08894495666027069</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.003765196306630969</v>
+        <v>0.1327770948410034</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0008714115829207003</v>
+        <v>0.06015182659029961</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.001488008652813733</v>
+        <v>0.04730185493826866</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.00367676792666316</v>
+        <v>0.07568366080522537</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001686232862994075</v>
+        <v>0.04523791372776031</v>
       </c>
       <c r="CU13" t="n">
-        <v>4.045186869916506e-07</v>
+        <v>0.03770837932825089</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001227673492394388</v>
+        <v>0.003194557502865791</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0005759921041317284</v>
+        <v>0.156205028295517</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0001284845930058509</v>
+        <v>0.009927567094564438</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.002946464810520411</v>
+        <v>0.08921858668327332</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.002073074458166957</v>
+        <v>0.03403580561280251</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.002274716040119529</v>
+        <v>0.009166033938527107</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001047754922183231</v>
+        <v>0.01877748593688011</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0002307929389644414</v>
+        <v>0.00807480700314045</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0003464996698312461</v>
+        <v>0.05038056522607803</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001264972612261772</v>
+        <v>0.03045654855668545</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.008947566151618958</v>
+        <v>0.06540799140930176</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.003505128202959895</v>
+        <v>0.0615963488817215</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.007630012463778257</v>
+        <v>0.1330185979604721</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.00284630386158824</v>
+        <v>0.03744508326053619</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0009197794133797288</v>
+        <v>0.03622521460056305</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001205693697556853</v>
+        <v>0.17718605697155</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.002586270682513714</v>
+        <v>0.1529903709888458</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.000438264396507293</v>
+        <v>0.01116310339421034</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.003427519463002682</v>
+        <v>0.05787072330713272</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0004456953029148281</v>
+        <v>0.06305820494890213</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.001508941408246756</v>
+        <v>0.0206258837133646</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.004841572139412165</v>
+        <v>0.05611088126897812</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.003494894364848733</v>
+        <v>0.01856478303670883</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.002324451459571719</v>
+        <v>0.02529936283826828</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.002175886183977127</v>
+        <v>0.005701806396245956</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0002020107640419155</v>
+        <v>0.1025822088122368</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.001879470772109926</v>
+        <v>0.1856114864349365</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.00151087692938745</v>
+        <v>0.08863703161478043</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0005916439113207161</v>
+        <v>0.01916364952921867</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.182970097754151e-05</v>
+        <v>0.01813895255327225</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.001727420138195157</v>
+        <v>0.009196601808071136</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.001578939496539533</v>
+        <v>0.08839373290538788</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.00102900667116046</v>
+        <v>0.1301063448190689</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.001694543519988656</v>
+        <v>0.08715734630823135</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002460907853674144</v>
+        <v>0.0945500060915947</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.003192240837961435</v>
+        <v>0.1229484081268311</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.001162428525276482</v>
+        <v>0.05533809214830399</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0009491678792983294</v>
+        <v>0.1409235596656799</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0004045457171741873</v>
+        <v>0.07160820066928864</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0008550224592909217</v>
+        <v>0.03455627709627151</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0004557787906378508</v>
+        <v>0.09379090368747711</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.00237265694886446</v>
+        <v>0.03473774343729019</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0007479953346773982</v>
+        <v>0.0160380732268095</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.001270082197152078</v>
+        <v>0.01601894572377205</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0004736649570986629</v>
+        <v>0.04700497165322304</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.002106410916894674</v>
+        <v>0.04670971632003784</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0008644356857985258</v>
+        <v>0.1384594142436981</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.001184642198495567</v>
+        <v>0.03314973413944244</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0007839989848434925</v>
+        <v>0.08737700432538986</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.003133983816951513</v>
+        <v>0.06794352829456329</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.006928705610334873</v>
+        <v>0.01582260616123676</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0006053439574316144</v>
+        <v>0.001249540131539106</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0002881091786548495</v>
+        <v>0.06638150662183762</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.000868246250320226</v>
+        <v>0.04161525517702103</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001827905653044581</v>
+        <v>0.005755555350333452</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0005554331000894308</v>
+        <v>0.179076299071312</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001383994822390378</v>
+        <v>0.005470274016261101</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0028814144898206</v>
+        <v>0.1214739084243774</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001299245283007622</v>
+        <v>0.02416327409446239</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.002153939101845026</v>
+        <v>0.007889559492468834</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001872443972388282</v>
+        <v>0.01278785616159439</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0001787089859135449</v>
+        <v>0.009264742955565453</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0002644954656716436</v>
+        <v>0.03737824782729149</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.002473545493558049</v>
+        <v>0.005256839096546173</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.001909372047521174</v>
+        <v>0.0947737917304039</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001270174980163574</v>
+        <v>0.07143326103687286</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0006377266836352646</v>
+        <v>0.1145959571003914</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001401647750753909</v>
+        <v>0.01017151586711407</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.001209316891618073</v>
+        <v>0.1251022666692734</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0004822304472327232</v>
+        <v>0.004787201061844826</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0005288008833304048</v>
+        <v>0.0001668240875005722</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.002331100171431899</v>
+        <v>0.1494866460561752</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.002258549677208066</v>
+        <v>0.05436592921614647</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.003029996529221535</v>
+        <v>0.1885753571987152</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.003675574902445078</v>
+        <v>0.1163517087697983</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0002926423621829599</v>
+        <v>0.06614460051059723</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.001593897119164467</v>
+        <v>0.05904572829604149</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0006660125218331814</v>
+        <v>0.02603726461529732</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0009609741391614079</v>
+        <v>0.00665800366550684</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0009356634691357613</v>
+        <v>0.1375214904546738</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0008974420488812029</v>
+        <v>0.06897652149200439</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001508664339780807</v>
+        <v>0.06558173894882202</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.001703290618024766</v>
+        <v>0.09100048243999481</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.001542625715956092</v>
+        <v>0.01693427562713623</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0007301957812160254</v>
+        <v>0.04899423196911812</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.003409279976040125</v>
+        <v>0.1600693762302399</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.002481191186234355</v>
+        <v>0.05843543261289597</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.001226006075739861</v>
+        <v>0.001853013411164284</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.004305345937609673</v>
+        <v>0.07984332740306854</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.002462134696543217</v>
+        <v>0.01593847759068012</v>
       </c>
     </row>
   </sheetData>
